--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -14,13 +14,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要介護度別の見込量" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_利用回（日）数" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_給付費の見込み" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_施設・居住系と定員" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_地域支援事業" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_中長期推計" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_給付費と保険料" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_据え置き・既定値" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_自己点検" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_確認事項" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_要介護度別の給付費" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_在宅と施設の連鎖" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_施設・居住系と定員" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_供給の制約と定員" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_地域支援事業" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_中長期推計" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_給付費と保険料" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_報酬改定率の感度" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_据え置き・既定値" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_自己点検" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_確認事項" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -143,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,6 +225,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -606,7 +616,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを11シートに残らず掲げています。受託者の算定であり確定値ではありません。（基準日 令和8年9月15日）</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを15シートに残らず掲げています。受託者の算定であり確定値ではありません。（基準日 令和8年9月15日）</t>
         </is>
       </c>
     </row>
@@ -711,7 +721,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>09シート</t>
+          <t>12シート</t>
         </is>
       </c>
     </row>
@@ -731,266 +741,346 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>11シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の給付費</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>総括表詳細（４）は要介護度別の内訳を持ちません。計画作成支援ツールの要介護度別の1人1月あたり給付費から「形」を採り、年報の要介護度別の利用者数で加重した平均が総括表の単価と一致するよう比例調整しました。基準年度では総括表の給付費を円単位で再現します。要介護度の構成が重度側へ動く分だけ平均の単価が上がります（令和11年度＋0.047％・令和22年度＋0.280％）。</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>07シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの率の分母の特定</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>実績値から逆算しました。総括表詳細（２）と管理指標D32の分母は第1号被保険者数、将来推計の在宅サービス利用率の分母は認定者数から施設・居住系サービス利用者数を引いた残余です。見込量を算定するための利用率の分母は認定者数であり、第1号被保険者数ではありません。取り違えると伸びが認定者数の伸びから第1号被保険者数の伸びへ置き換わります。</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
           <t>08シート</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>供給の制約（定員上限）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.116として据え置いていたものに着手しました。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達し、令和17年度には超えます。第10期の間は超過が生じないため見込量は動きません。人材・受入可能量・休廃止の意向はなお反映していません。</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>報酬改定率の感度</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>改定率1％あたり月額＋61円です。趨勢に現れない要因の分析（＋61円）と一致します。単価の趨勢（年率1.75％）を織り込む案と重ねると二重になるため、どちらか一方によることをご判断いただく必要があります。</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>14シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2　算定の式</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>式</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>固定したもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>要介護度別の認定者数</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>年齢階級別の認定者数（シナリオ②）× 年齢階級ごとの要介護度の構成</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>構成は令和7年度末の実績で固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>見込量（人／月）</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度の要介護度別の月平均利用者数 × 要介護度別の認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>要介護度別の利用率は令和7年度で固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>利用回（日）数（回・日／月）</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>見込量 × 1人1月あたり利用回（日）数</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>回（日）数は令和7年度で固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>給付費（円）</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>見込量 × 12 × 1人あたり給付費</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>単価は令和7年度で固定（報酬改定率が未公表のため）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>標準給付費見込額（A）</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>総給付費 × 割増率1.05909</t>
+          <t>年齢階級別の認定者数（シナリオ②）× 年齢階級ごとの要介護度の構成</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算による</t>
+          <t>構成は令和7年度末の実績で固定</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>保険料収納必要額（J）</t>
+          <t>見込量（人／月）</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C＋D－E＋F＋G±H－I</t>
+          <t>令和7年度の要介護度別の月平均利用者数 × 要介護度別の認定者数の伸び</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>F・G・Hはいずれも0</t>
+          <t>要介護度別の利用率は令和7年度で固定</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数（回・日／月）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>見込量 × 1人1月あたり利用回（日）数</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>回（日）数は令和7年度で固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>給付費（円）</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>見込量 × 12 × 1人あたり給付費</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>単価は令和7年度で固定（報酬改定率が未公表のため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額（A）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>総給付費 × 割増率1.05909</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算による</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納必要額（J）</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C＋D－E＋F＋G±H－I</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>F・G・Hはいずれも0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>算定上の月額基準額</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>J ÷ 予定収納率 ÷ 補正後被保険者数 ÷ 12</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>予定収納率99.0％・第1号負担割合23％</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>3　算定の結果</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>第10期の総給付費（3か年計）</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>算定上の月額基準額</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="n">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>本表（要介護度別）</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>9,031,900,444円</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>6,436円</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="n">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>参考　一律の伸び（従前のP3）</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>9,020,228,881円</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>6,428円</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="5" t="n">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>参考　現行（見える化の自然体推計×案C補正・P1）</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>9,483,461,997円</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>6,740円</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="31" ht="62" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>注1）月額は算定上の月額基準額です。条例で定める基準額ではありません。第9期は算定上6,428円・条例6,400円です。
 注2）本表は保険料の採用値を定めるものではありません。採用値のご判断をお願いする材料です。
-注3）据え置いたものは11シートに20件掲げています。うち月額を100円以上動かし得るものがあります。
+注3）据え置いたものは15シートに23件掲げています。うち月額を100円以上動かし得るものがあります。
 注4）保険料は介護保険法第3条及び地方自治法第284条により保険者（広域連合）を単位として算定します。町別には算定しません。</t>
         </is>
       </c>
@@ -998,17 +1088,2554 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>施設・居住系サービスと必要利用定員総数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>施設・居住系サービスの見込量を定員と対比します。必要利用定員総数（法第117条第2項第1号）は3町の整備方針が確定していないため、現に指定を受けている定員を据え置く案を掲げます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　施設・居住系サービスの見込量と定員</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R7実績
+（人／月）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>R11／定員</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>定員の出所</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>90.4％</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>北海道 特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>99.9％</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>137</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>58.4％</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧（3施設）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>区域内に事業所なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>介護療養型医療施設</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>区域内に事業所なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>41.1％</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧。類型（混合型・介護専用型）は［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>区域内に事業所なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>86.1％</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>99人＋［要確認］（東川町の1事業所が未確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="94" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>注1）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の在籍者とは数える対象が違います。調査②（施設調査）では特別養護老人ホーム等の在籍者146人に対し年報の受給者は197.5人／月であり、区域外の施設の利用が含まれます（調査結果と年報実績の突合 確認事項No.141）。したがって定員に対する率が100％を超えることがあります。
+注2）介護老人保健施設は令和7年度130人／月から令和8年度111人／月へ14.6％減少しています（確認事項No.133）。定員は平成27年度から3施設240人で不変です。本表は令和7年度を基準としており、この減少を将来へ延長していません。
+注3）特定施設入居者生活介護の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2　必要利用定員総数（日常生活圏域ごと）　据え置き案</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>日常生活圏域</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>現況（令和8年度）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>36＋［要確認］（3）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>36＋［要確認］</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>36＋［要確認］</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>36＋［要確認］</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>0（0）</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0（0）</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>27（2）</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0（0）</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>42（2）</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>36（2）</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>0（0）</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>20（1）</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>99＋［要確認］（7）</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>99＋［要確認］</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>99＋［要確認］</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>99＋［要確認］</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>0（0）</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>62（3）</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>第10期中の整備を見込まない（据え置き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>注1）これは据え置き案であり確定値ではありません。計画素案 第6章第4節4の本文は［要協議］のまま残しています。東川町は令和8年10月に施設整備・サービス提供方針を、東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しています（確認事項No.84・No.88）。
+注2）第10期中に整備の予定がない圏域は「0」と記載します。整備しないことも計画上の判断として記載するものです。
+注3）認知症対応型共同生活介護の定員は、北海道の名簿では7事業所108人、見える化システムD26（令和6年度）では5事業所99人であり一致しません。現に指定を受けている定員を3町への照会により確定する必要があります。
+注4）混合型特定施設入居者生活介護に係る必要利用定員総数を定めるかどうかは確認事項No.113です。特定施設の類型が未確認であるため定めていません。
+注5）区域内の施設の定員と保険者の受給者は一致しません（注1・1の表）。必要利用定員総数は区域内の施設の定員により定めるものであり、見込量（保険者の被保険者の受給）とは別に整理します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>3　令和9年4月新設のサービス区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>登録施設介護支援・登録施設介護予防支援</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>実績がないため0として立てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>特定地域サービス</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>実績がないため0として立てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>特定地域居宅サービス等事業</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>実績がないため0として立てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>注）見える化システムのサービス一覧には「登録施設介護支援」が既に現れています（全年度0.00％）。移行の範囲と単価が示されるまで見込量を0として立て、区分だけを掲げます（確認事項No.115）。夜間対応型訪問介護の区分もなお残っています。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>供給の制約（定員上限）と在宅への振替</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>見込量は需要の側だけで置いており、供給の制約を課していません（確認事項No.116）。区域内の定員を超えて増えないものとした場合に何が起きるかを示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　定員に対する到達率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R7実績</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>R11／定員</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>定員に達する年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>90.4％</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>99.9％</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>58.4％</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>41.1％</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>86.1％</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達します。**令和17年度には定員を超えます。介護老人福祉施設も令和22年度に定員を超えます。
+注2）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の定員は当連合の被保険者にとっての上限ではなく、区域外の施設の利用により定員を超える受給が生じ得ます（確認事項No.141）。したがって到達率が100％を超えることは誤りではありません。ただし区域内で受け止めるのであれば整備を要します。
+注3）介護老人保健施設（58.4％）・特定施設入居者生活介護（41.1％）は定員に余裕があります。特定施設の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］
+注4）認知症対応型共同生活介護の定員は99人＋［要確認］です。東川町の1事業所の定員が未確定であるため、到達率は上側に振れています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　定員で頭打ちにした場合の在宅への振替</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>施設・居住系（需要）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>定員超過分</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>頭打ち後の施設・居住系</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>在宅の認定者数（需要）</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>頭打ち後の在宅の認定者数</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>増加率</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1534.3</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1534.3</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>+0.00％</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>超過なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>1549.9</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>1549.9</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>+0.00％</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>超過なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>1565.8</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1565.8</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>+0.00％</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>超過なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>541.6</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>1680.7</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1686.3</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>+0.33％</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>超過分が在宅へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>563.9</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>553.1</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>1724.2</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1735</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>+0.63％</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>超過分が在宅へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>注1）第10期（令和9〜11年度）では超過が生じません。定員上限を課しても見込量は動きません。
+注2）令和22年度では10.8人が超過し、在宅の認定者数が0.63％増えます。中長期の見込みでは供給の制約が効きはじめます。
+注3）在宅へ戻った分がどのサービスへ向かうかは、在宅サービスの利用率を掛けて配分することになります。本表はその配分を行っていません。施設に入れない方の在宅サービスの使い方が在宅の平均と同じであるとは限らないためです。［要協議］
+注4）**本表の採用値は頭打ちを課さないものとしています。**第10期では差がなく、また区域外の施設の利用により定員を超える受給が生じ得るためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>3　供給の制約のうち反映していないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>制約</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>人材</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>介護職員・看護職員の確保の見通し。見える化M系列の従業員総数はあるが、将来の確保可能量は調査していない</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>反映していない（確認事項No.116）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>受入可能量</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>定員があっても、職員の不足により実際には受け入れられない床がある。事業所への意向調査を行っていない</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>反映していない。定員をそのまま上限としている</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>休止・廃止の意向</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>事業所の休止・廃止・縮小の意向を把握していない</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>反映していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>区域外の施設の受入れ</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>当連合の被保険者の区域外利用は年報に含まれるが、区域外の施設に受け入れる余力があるかは分からない</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>現状の利用の続くことを前提としている</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>住所地特例</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>年報様式1で77人と分かるが、住所地特例に当たらない区域外利用は分けられない</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>分けずに算定している（確認事項No.141）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地域支援事業の量と費用の見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。令和7年度の実績が未受領であるため令和6年度の実績を基礎とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　介護予防・日常生活支援総合事業の量の見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R6実績
+（3町計）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>延ばし方</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>訪問型サービス（従前相当）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービス（従前相当）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスA　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスC　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>その他生活支援（配食）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>その他生活支援（複合的提供）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントA　実施件数</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>203.1</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントC　実施件数</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>基本チェックリスト実施者数</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>245.3</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の伸び</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2　一般介護予防事業（通いの場）の量の見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>R6実績
+（3町計）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>延ばし方</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　箇所数</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>据え置き</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績による</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　参加者実人数</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の伸び</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績による</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　週1回以上の箇所数</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>据え置き</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績による</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数で延ばすものではありません。令和6年度の実績（25箇所）を据え置きました。目標値を置く場合は3町のご意向によります［要協議］。
+注2）参加者実人数の割合（第1号被保険者に対する）は代表KPI H05の指標です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>3　地域支援事業費の見込み（円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>R6実績</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>第10期計</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>321,387,954</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール（3町計）。令和7年度実績は未受領のため据え置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業及び任意事業費</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>175,804,914</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（保険料算定上のB）</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>177,161,259</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>177,161,259</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>177,161,259</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>177,161,259</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>531,483,777</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算（款4）から保険者機能強化推進事業費及び保険者努力支援事業費を除いたもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="68" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>注1）総合事業費は決算科目の「介護予防・生活支援サービス事業費」101,274,621円と5,854,697円の差があります。決算（広域連合の款項）と計画作成支援ツール（3町入力）で基礎が異なることによります。［要確認］
+注2）地域支援事業費（B）から2事業を除く方法を採っており、保険料収納必要額からの交付見込額の控除は行っていません。両者を併用すると二重控除になります（確認事項No.86）。控除する方法に改める場合はBを款4の全体183,384,259円に戻します。
+注3）令和7年度の総合事業の実績の提供を受けた時点で置き直します（資料提供依頼No.13）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1563,7 +4190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2417,7 +5044,7 @@
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>注1）第9期は財政調整基金40,000,000円を取り崩しています。本表は取崩しを行わないものとしています。同額を取り崩せば月額は約▲124円となります。
-注2）据え置いたもの（11シート）のうち、報酬改定率と単価の趨勢は月額を＋185〜＋374円動かし得ます。本表の月額はこれを含まない下側の値です。
+注2）据え置いたもの（15シート）のうち、報酬改定率と単価の趨勢は月額を＋185〜＋374円動かし得ます。本表の月額はこれを含まない下側の値です。
 注3）第1号被保険者負担割合を23％で置いています。1ポイントの違いで月額が約290円動きます。［要確認］</t>
         </is>
       </c>
@@ -2435,13 +5062,386 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>報酬改定率の感度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和9年度は介護報酬改定の年に当たります（3年周期）。改定率が未公表であるため単価を令和7年度で固定していますが、改定率を一律に乗じた場合に月額がどこまで動くかを示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　改定率を単価に一律に乗じた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>改定率</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度（円）</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度（円）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度（円）</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>第10期計（百万円）</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>月額（円）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>本表との差</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>+0％</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>2,978,267,893</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>3,010,470,894</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>3,043,161,657</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>9031.9</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>6436</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>+0円</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>+1％</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>3,008,050,572</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>3,040,575,602</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>3,073,593,274</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9122.200000000001</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6497</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>+61円</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>+2％</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3,037,833,251</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>3,070,680,311</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>3,104,024,890</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9212.5</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>6558</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>+122円</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>+3％</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>3,067,615,930</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>3,100,785,020</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>3,134,456,507</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9302.9</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6619</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>+182円</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>注1）改定率1％あたり月額+61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
+注2）**改定は令和9年度の1回だけを見ています。**第10期中の改定は令和9年度のみです（次は令和12年度）。
+注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
+注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2　単価の趨勢を織り込んだ場合（参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>置き方</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>第10期計（百万円）</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>月額（円）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>本表との差</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>単価固定（本表）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>9031.9</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>6436</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>+0円</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度の実績単価をそのまま用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>年率1.75％を2年分（令和7→9年度）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9348</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6649</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+213円</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>連鎖ラスパイレス指数による単価の趨勢</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>年率1.75％を各年度に複利で</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>9516.6</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>6762</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>+326円</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度＋3.53％・令和10年度＋5.34％・令和11年度＋7.22％</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>注）単価の趨勢と報酬改定は別のものではありません。改定のあった年となかった年で単価の伸びに差が見られないため、改定率を乗じることと趨勢を延ばすことを重ねると二重になります。どちらか一方によることをご判断いただく必要があります。［要協議］確認事項No.110・No.137</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2521,7 +5521,7 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>令和7年度の実績単価で固定した</t>
+          <t>令和7年度の実績単価で固定した。改定率を乗じた場合の感度を14シートに示した</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -2541,32 +5541,32 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり利用回（日）数</t>
+          <t>要介護度別の単価</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>要介護度別の1人1月あたり給付費（保険者単位）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>同上。回数の趨勢は年率＋0.25％（中央値）にとどまる</t>
+          <t>総括表詳細（４）は要介護度別の内訳を持たない。計画作成支援ツールは要介護度別を持つが3町合計である</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>令和7年度の実績で固定した</t>
+          <t>ツールから要介護度間の比（形）だけを採り、水準は総括表に合わせて比例調整した。採用値は単価固定（06シート）のままとし、07シートに別掲した</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>No.110</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>回数のみでは月額への効きは小さい</t>
+          <t>要介護度別の単価を用いると令和11年度＋0.047％（月額＋2円）、令和22年度＋0.280％</t>
         </is>
       </c>
     </row>
@@ -2576,32 +5576,32 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>要介護度の構成</t>
+          <t>1人1月あたり利用回（日）数</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の将来推計</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>国の様式も見える化システムも要介護度別の推計を出力しない</t>
+          <t>同上。回数の趨勢は年率＋0.25％（中央値）にとどまる</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される</t>
+          <t>令和7年度の実績で固定した</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>No.110</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額+8円</t>
+          <t>回数のみでは月額への効きは小さい</t>
         </is>
       </c>
     </row>
@@ -2611,32 +5611,32 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）</t>
+          <t>要介護度の構成</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>第10期の地域支援事業費の見込み</t>
+          <t>要介護度別の将来推計</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>3町の事業計画が未確定である</t>
+          <t>国の様式も見える化システムも要介護度別の推計を出力しない</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>令和6年度決算額（保険者機能強化推進事業費及び保険者努力支援事業費を除く）を3年据え置いた</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>No.86</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>交付見込額の控除方法によって動く（確認事項No.86）</t>
+          <t>一律の伸びとの差は月額+8円</t>
         </is>
       </c>
     </row>
@@ -2646,32 +5646,32 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>総合事業費</t>
+          <t>地域支援事業費（B）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の総合事業の実績</t>
+          <t>第10期の地域支援事業費の見込み</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>未受領である（資料提供依頼No.13）</t>
+          <t>3町の事業計画が未確定である</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>令和6年度の計画作成支援ツールの値（3町計107,129,318円）を3年据え置いた</t>
+          <t>令和6年度決算額（保険者機能強化推進事業費及び保険者努力支援事業費を除く）を3年据え置いた</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>No.112</t>
+          <t>No.86</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎に入る。差5,854,697円で月額約▲7円</t>
+          <t>交付見込額の控除方法によって動く（確認事項No.86）</t>
         </is>
       </c>
     </row>
@@ -2681,22 +5681,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>総合事業の量の見込み</t>
+          <t>総合事業費</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>令和7年度の総合事業の実績</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>同上。令和6年度の実施状況調査は受領済みである</t>
+          <t>未受領である（資料提供依頼No.13）</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>令和6年度の実施状況調査の実績を基礎とし、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びで延ばした</t>
+          <t>令和6年度の計画作成支援ツールの値（3町計107,129,318円）を3年据え置いた</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -2706,7 +5706,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>給付費には入らない（保険料への効きはない）</t>
+          <t>調整交付金の算定基礎に入る。差5,854,697円で月額約▲7円</t>
         </is>
       </c>
     </row>
@@ -2716,32 +5716,32 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数</t>
+          <t>総合事業の量の見込み</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>3町の施設整備方針</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>東川町は令和8年10月、東神楽町は令和8年10月・11月に検討を予定している</t>
+          <t>同上。令和6年度の実施状況調査は受領済みである</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>現に指定を受けている定員を第10期を通じて据え置く案を掲げた。計画素案の本文は［要協議］のまま残している</t>
+          <t>令和6年度の実施状況調査の実績を基礎とし、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びで延ばした</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>No.88・No.84</t>
+          <t>No.112</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>整備を行えば見込量と給付費が動く</t>
+          <t>給付費には入らない（保険料への効きはない）</t>
         </is>
       </c>
     </row>
@@ -2751,32 +5751,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員</t>
+          <t>必要利用定員総数</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>3町への照会（東川町の1事業所）</t>
+          <t>3町の施設整備方針</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>くるみの郷（東川町）は介護サービス情報公表システムに掲載がない</t>
+          <t>東川町は令和8年10月、東神楽町は令和8年10月・11月に検討を予定している</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>判明している99人に［要確認］を併記した</t>
+          <t>現に指定を受けている定員を第10期を通じて据え置く案を掲げた。計画素案の本文は［要協議］のまま残している</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>No.88</t>
+          <t>No.88・No.84</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>定員の確定は必要利用定員総数の前提</t>
+          <t>整備を行えば見込量と給付費が動く</t>
         </is>
       </c>
     </row>
@@ -2786,32 +5786,32 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員の縮小</t>
+          <t>認知症対応型共同生活介護の定員</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>特別養護老人ホームの定員の経緯</t>
+          <t>3町への照会（東川町の1事業所）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>平成29年234人から令和2年以降160人への縮小の経緯が未確認である</t>
+          <t>くるみの郷（東川町）は介護サービス情報公表システムに掲載がない</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>令和7年度の実績を基礎とし、定員の縮小を将来へ延長しない（安全側）</t>
+          <t>判明している99人に［要確認］を併記した</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>No.107</t>
+          <t>No.88</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>縮小を延長すると給付費が下がり保険料が不足する側に誤る</t>
+          <t>定員の確定は必要利用定員総数の前提</t>
         </is>
       </c>
     </row>
@@ -2821,32 +5821,32 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正</t>
+          <t>施設・居住系の定員の縮小</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>補正を行うかどうかのご判断</t>
+          <t>特別養護老人ホームの定員の経緯</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.106が未決着である</t>
+          <t>平成29年234人から令和2年以降160人への縮小の経緯が未確認である</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>補正を行わない（一律の伸び）。本表はサービス別の伸びの差を織り込んでいない</t>
+          <t>令和7年度の実績を基礎とし、定員の縮小を将来へ延長しない（安全側）</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>No.106</t>
+          <t>No.107</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>補正のみで月額▲58円、施設・居住系を減らさない条件を加えると＋48円</t>
+          <t>縮小を延長すると給付費が下がり保険料が不足する側に誤る</t>
         </is>
       </c>
     </row>
@@ -2856,32 +5856,32 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>季節補正</t>
+          <t>対計画比の偏りの補正</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>補正を行うかどうかのご判断</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3は令和7年度（完結年度）を基準とする</t>
+          <t>確認事項No.106が未決着である</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない</t>
+          <t>補正を行わない（一律の伸び）。本表はサービス別の伸びの差を織り込んでいない</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>No.103</t>
+          <t>No.106</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>効きは0円</t>
+          <t>補正のみで月額▲58円、施設・居住系を減らさない条件を加えると＋48円</t>
         </is>
       </c>
     </row>
@@ -2891,32 +5891,32 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>施策の反映</t>
+          <t>季節補正</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>施策の達成目標のご判断</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.105が未決着である</t>
+          <t>採用パターンP3は令和7年度（完結年度）を基準とする</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>施策による見込量の増減を織り込まない（自然体）</t>
+          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>No.105</t>
+          <t>No.103</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>数値を置ける施策は定期巡回の整備のみで月額＋2〜＋13円</t>
+          <t>効きは0円</t>
         </is>
       </c>
     </row>
@@ -2926,32 +5926,32 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制</t>
+          <t>施策の反映</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第7期給付適正化計画の目標のご判断</t>
+          <t>施策の達成目標のご判断</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.93・No.110が未決着である</t>
+          <t>確認事項No.105が未決着である</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>抑制を織り込まない（安全側）</t>
+          <t>施策による見込量の増減を織り込まない（自然体）</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>No.93</t>
+          <t>No.105</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>対象4サービスは総給付費の7.70％。10％抑制でも月額▲47円</t>
+          <t>数値を置ける施策は定期巡回の整備のみで月額＋2〜＋13円</t>
         </is>
       </c>
     </row>
@@ -2961,32 +5961,32 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者負担割合</t>
+          <t>給付適正化による抑制</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令</t>
+          <t>第7期給付適正化計画の目標のご判断</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>未公布である</t>
+          <t>確認事項No.93・No.110が未決着である</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>第9期と同じ23％で置いた</t>
+          <t>抑制を織り込まない（安全側）</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>No.33</t>
+          <t>No.93</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>1ポイントの違いで月額が約290円動く</t>
+          <t>対象4サービスは総給付費の7.70％。10％抑制でも月額▲47円</t>
         </is>
       </c>
     </row>
@@ -2996,32 +5996,32 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>予定保険料収納率</t>
+          <t>第1号被保険者負担割合</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期の収納率のご判断</t>
+          <t>第10期の政令</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>未決着である</t>
+          <t>未公布である</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>第9期と同じ99.0％で置いた</t>
+          <t>第9期と同じ23％で置いた</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>No.33</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>0.1ポイントで月額約6円</t>
+          <t>1ポイントの違いで月額が約290円動く</t>
         </is>
       </c>
     </row>
@@ -3031,22 +6031,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>基金の取崩し</t>
+          <t>予定保険料収納率</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>令和7年度末の基金残高</t>
+          <t>第10期の収納率のご判断</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>未受領である</t>
+          <t>未決着である</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>取崩しを行わない（I＝0）</t>
+          <t>第9期と同じ99.0％で置いた</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -3056,7 +6056,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>1億円の取崩しで月額約▲310円</t>
+          <t>0.1ポイントで月額約6円</t>
         </is>
       </c>
     </row>
@@ -3066,32 +6066,32 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>所得段階別加入割合補正</t>
+          <t>基金の取崩し</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期の所得段階の政令改正</t>
+          <t>令和7年度末の基金残高</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>未公布である</t>
+          <t>未受領である</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>令和6年度の実績による係数で置いた</t>
+          <t>取崩しを行わない（I＝0）</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>No.33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>補正後被保険者数を通じて効く</t>
+          <t>1億円の取崩しで月額約▲310円</t>
         </is>
       </c>
     </row>
@@ -3101,32 +6101,32 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設のサービス区分</t>
+          <t>所得段階別加入割合補正</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>施行に伴う省令・様式</t>
+          <t>第10期の所得段階の政令改正</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>登録施設介護（予防）支援・特定地域サービス・特定地域居宅サービス等事業は令和9年4月新設である</t>
+          <t>未公布である</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>実績がないため見込量を0として立て、区分だけを掲げた</t>
+          <t>令和6年度の実績による係数で置いた</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>No.115</t>
+          <t>No.33</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>移行の範囲が示されるまで給付費に影響しない</t>
+          <t>補正後被保険者数を通じて効く</t>
         </is>
       </c>
     </row>
@@ -3136,32 +6136,32 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数</t>
+          <t>令和9年4月新設のサービス区分</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>特定施設の類型（混合型・介護専用型）</t>
+          <t>施行に伴う省令・様式</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>区域内4事業所の類型が未確認である</t>
+          <t>登録施設介護（予防）支援・特定地域サービス・特定地域居宅サービス等事業は令和9年4月新設である</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>定員156人を据え置き、類型は［要確認］とした</t>
+          <t>実績がないため見込量を0として立て、区分だけを掲げた</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>No.113</t>
+          <t>No.115</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>定めるかどうかの判断が先</t>
+          <t>移行の範囲が示されるまで給付費に影響しない</t>
         </is>
       </c>
     </row>
@@ -3171,39 +6171,144 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）</t>
+          <t>混合型特定施設の必要利用定員総数</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>事業所の受入可能量・従事者数の見通し</t>
+          <t>特定施設の類型（混合型・介護専用型）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
+          <t>区域内4事業所の類型が未確認である</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>定員156人を据え置き、類型は［要確認］とした</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>No.113</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>定めるかどうかの判断が先</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>供給の制約（定員上限）</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>3町の施設整備方針</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>定員は把握しているが、第10期中に整備を行うかが未確定である</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>定員上限を課さずに算定した。課した場合の在宅への振替を10シートに示した。第10期（令和9〜11年度）は超過が生じないため見込量は動かない</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>No.88</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>第10期は0円。令和22年度では10.8人が超過する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>供給の制約（人材・受入可能量）</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>事業所の受入可能量・従事者数の見通し・休廃止の意向</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
           <t>調査していない</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>需要のみで見込量を置いた（供給制約を課さない）</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>No.116</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>制約を課せば見込量は下がる</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="76" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>注1）20件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋185〜＋374円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>施設に入れない方の在宅サービスの使い方</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>施設の待機者の在宅サービスの利用の状況</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>調査していない。定員で頭打ちになった分がどのサービスへ向かうかは在宅の平均と同じとは限らない</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>在宅への振替の配分を行っていない（10シート）</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>No.88</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>第10期は振替が生じないため0円</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>注1）23件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋185〜＋374円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
 注2）安全側に置いたもの（保険料が不足する側に誤らないようにしたもの）は3件です。施策の反映を織り込まない、給付適正化による抑制を織り込まない、施設・居住系の定員の縮小を将来へ延長しない、の3件です。
 注3）対計画比は第7期からの8年度すべてで100％未満（8年平均94.93％）であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため、同じ偏りを持ち得ます（確認事項No.106）。</t>
         </is>
@@ -3211,21 +6316,21 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3482,7 +6587,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06シートの給付費の合計と10シートの総給付費の一致</t>
+          <t>06シートの給付費の合計と13シートの総給付費の一致</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3587,7 +6692,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>23件</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -3651,153 +6756,328 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
-      <c r="B20" s="11" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の単価による令和7年度の給付費と総括表の一致</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2,915,307,125円</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>差 0.0000円</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の単価が得られない種別が実績0の種別と一致すること</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>単価なし6種別</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>実績0 6種別。両者は同じ</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>見える化の在宅サービス利用率の分母が在宅の認定者数に当たること</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>逆算した分母の中央値 1502.3人</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>当方の在宅の認定者数 1503.8人（差 0.1％）</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>総括表詳細（２）の分母がサービスによらず第1号被保険者数に当たること</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>逆算 9123.2／9123.3／9123.3</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>総括表の第1号被保険者数 9,119人（差 0.05％）</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>第10期（令和9〜11年度）に定員の超過が生じないこと</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>定員を掲げた5種別</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>超過 0.0／0.0／0.0人</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>報酬改定率1％あたりの月額が趨勢に現れない要因の分析と一致すること</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>60.8円</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>同分析の＋61円と一致</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>総括表とツールの対応表を `build_mikomiryo.py` から読めていること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>TOOLMAP 23行</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>固定値を書き写していない</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>15件</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>適合15件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>22件</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>適合22件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>点検の対象としていないもの</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="5" t="n">
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>見込量の水準そのもの</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>対計画比は第7期からの8年度すべてで100％未満であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため同じ偏りを持ち得ます（確認事項No.106）</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>3町合計と広域連合単位の給付費の差（令和7年度4.0％）</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>確認事項No.87として照会中です。本表は広域連合単位（年報）によります</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>報酬改定率</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>未公表であるため単価を令和7年度で固定しました（確認事項No.110）</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>必要利用定員総数の水準</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>3町の整備方針が確定していないため、据え置き案を掲げるにとどめています</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>総合事業の量の令和7年度実績</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>未受領です。令和6年度の実施状況調査を据え置いています（確認事項No.112）</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3910,7 +7190,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>同項はR9〜R11が空欄で「量」の表自体がありません（確認事項No.112）。法第117条第2項第2号の基本的記載事項です。令和7年度の実績が未受領であるため、令和6年度の実施状況調査を基礎とした本表08シートによることとなります。</t>
+          <t>同項はR9〜R11が空欄で「量」の表自体がありません（確認事項No.112）。法第117条第2項第2号の基本的記載事項です。令和7年度の実績が未受領であるため、令和6年度の実施状況調査を基礎とした本表11シートによることとなります。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3935,7 +7215,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>改正法により令和22年度（2040年）を含む中長期の見込みが記載事項となります（確認事項No.114）。計画素案は認定者数までを掲げています。本表09シートにより見込量・給付費まで算定できます。</t>
+          <t>改正法により令和22年度（2040年）を含む中長期の見込みが記載事項となります（確認事項No.114）。計画素案は認定者数までを掲げています。本表12シートにより見込量・給付費まで算定できます。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -3960,7 +7240,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>3町の整備方針が確定していないため、本表07シートでは現に指定を受けている定員を第10期を通じて据え置く案を掲げています。計画素案の本文は［要協議］のまま残しています。東川町は令和8年10月、東神楽町は令和8年10月・11月に検討を予定しています（確認事項No.84・No.88）。</t>
+          <t>3町の整備方針が確定していないため、本表09シートでは現に指定を受けている定員を第10期を通じて据え置く案を掲げています。計画素案の本文は［要協議］のまま残しています。東川町は令和8年10月、東神楽町は令和8年10月・11月に検討を予定しています（確認事項No.84・No.88）。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4010,7 +7290,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13のうち未受領の部分です。本表08シートは令和6年度の実施状況調査を据え置いています。令和7年度の実績により置き直します。</t>
+          <t>資料提供依頼No.13のうち未受領の部分です。本表11シートは令和6年度の実施状況調査を据え置いています。令和7年度の実績により置き直します。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -4044,8 +7324,83 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ご判断</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>給付費を要介護度別の単価で算定してよいか</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>総括表詳細（４）は要介護度別の内訳を持たないため、計画作成支援ツールの要介護度別の1人1月あたり給付費から要介護度間の比（形）だけを採り、水準は総括表（保険者単位）に合わせて比例調整しました。基準年度では総括表の給付費を円単位で再現します。要介護度の構成が重度側へ動く分だけ平均の単価が上がり、令和11年度＋0.047％（月額＋2円）・令和22年度＋0.280％です。ツールは3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていません。本表の採用値は単価固定（06シート）のままとしています。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月30日まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>ご協議</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護が令和11年度に定員に達することへの対応</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>本表の見込みでは令和11年度に61.9人／月となり、区域内の定員62人の99.9％に達します。令和17年度には超えます。①区域外の施設の利用で受け止めるか、②整備するか、③見込量の側を定員で頭打ちにするかのご協議をお願いします。年報は施設の所在地を問わず当連合の被保険者を数えるため、区域内の定員は上限ではありません（確認事項No.141）。本表は頭打ちを課していません（第10期は差が生じません）。</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月26日まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>ご判断</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>報酬改定率と単価の趨勢のどちらによるか</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋185〜＋374円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月30日まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>注）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。計画素案の本文には確認事項の注記を書きません。</t>
         </is>
@@ -4054,8 +7409,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5079,7 +8434,7 @@
       <c r="A28" s="10" t="inlineStr">
         <is>
           <t>注1）要介護度別の伸びは一律ではありません。85歳以上の人口が増えることにより、85歳以上に多い要介護度の伸びが総数の伸びを上回ります。令和11年度で最も高いのは要介護3の1.0489、最も低いのは要支援1の1.0383です。
-注2）要介護度の構成そのもの（同じ年齢階級の中での構成）は令和7年度末の実績で固定しています。認知症の人の増加や医療の変化による構成の変化は反映していません（11シート）。
+注2）要介護度の構成そのもの（同じ年齢階級の中での構成）は令和7年度末の実績で固定しています。認知症の人の増加や医療の変化による構成の変化は反映していません（15シート）。
 注3）中長期（令和17年度・令和22年度）は令和11年度以降は認定率を固定し人口の変化のみで延ばしています。</t>
         </is>
       </c>
@@ -9457,7 +12812,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>見込量（人／月）に12と1人あたり給付費（令和7年度実績）を乗じたものです。報酬改定率が未公表であるため単価は固定しています（11シート）。</t>
+          <t>見込量（人／月）に12と1人あたり給付費（令和7年度実績）を乗じたものです。報酬改定率が未公表であるため単価は固定しています（15シート）。</t>
         </is>
       </c>
     </row>
@@ -11005,7 +14360,7 @@
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>注1）ここでいう給付費は総給付費であり、特定入所者介護サービス費・高額介護サービス費・審査支払手数料等を含みません。これらを加えたものが標準給付費見込額です（10シート）。
+          <t>注1）ここでいう給付費は総給付費であり、特定入所者介護サービス費・高額介護サービス費・審査支払手数料等を含みません。これらを加えたものが標準給付費見込額です（13シート）。
 注2）令和7年度の総給付費は2,915,307,125円です。第10期の3か年計は9,031,900,444円で、令和7年度の3年分に対し+3.3％です。
 注3）1人あたり給付費は延べ1人あたりの月額です。令和7年度の実績で固定しています。</t>
         </is>
@@ -11028,38 +14383,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>施設・居住系サービスと必要利用定員総数</t>
+          <t>要介護度別の給付費</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>施設・居住系サービスの見込量を定員と対比します。必要利用定員総数（法第117条第2項第1号）は3町の整備方針が確定していないため、現に指定を受けている定員を据え置く案を掲げます。</t>
+          <t>総括表詳細（４）は要介護度別の内訳を持ちません。計画作成支援ツールの要介護度別の1人1月あたり給付費から「形」を採り、年報の要介護度別の利用者数で加重した平均が総括表の単価と一致するよう比例調整しました。令和7年度では一致します（点検16）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　施設・居住系サービスの見込量と定員</t>
+          <t>1　要介護度別の1人1月あたり給付費（円。令和7年度）</t>
         </is>
       </c>
     </row>
@@ -11072,42 +14428,46 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>定員</t>
+          <t>要支援1</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>R7実績
-（人／月）</t>
+          <t>要支援2</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>令和9年度</t>
+          <t>要介護1</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>令和10年度</t>
+          <t>要介護2</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>令和11年度</t>
+          <t>要介護3</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>R11／定員</t>
+          <t>要介護4</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>定員の出所</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>調整係数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
@@ -11116,33 +14476,36 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>138.2</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>141.4</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>144.6</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>90.4％</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>北海道 特別養護老人ホーム名簿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>232145</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>251002</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>255732</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>276320</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>290912</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.9247</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
@@ -11151,33 +14514,36 @@
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>99.9％</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>273635</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>289661</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>281137</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>251964</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>342087</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
@@ -11186,33 +14552,36 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>134.1</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>140.1</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>58.4％</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧（3施設）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>273054</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>293240</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>317866</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>314061</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>299582</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.9552</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
@@ -11226,881 +14595,2239 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>区域内に事業所なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>337577</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>410307</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1.1641</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>57757</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>100376</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>159988</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>188637</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>209384</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>228887</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>238772</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.9285</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>271363</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>199815</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>276927</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>287787</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>289489</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>280527</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.9718</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>58441</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>90501</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>167727</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>220659</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>261186</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>97053</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>30387</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>44577</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>47688</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>97490</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.9141</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>39971</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>42452</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>39010</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>53202</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>63873</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>1.0782</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>17420</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>30277</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>28832</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>37029</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>43205</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>28723</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>39050</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0.9583</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>12200</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>12074</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>9655</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10439</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>9324</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>9190</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>10015</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>1.3306</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>54323</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>55345</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>78810</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>88943</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>81548</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.9614</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>48264</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>79009</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>114900</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>105655</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>27926</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>1.0156</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>21889</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>42861</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>51832</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>73602</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>82918</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>77737</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>85663</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0.931</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>17190</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>55817</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>79326</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>80976</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>128265</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>88420</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>112801</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>0.9313</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>27979</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>26059</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>49091</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>63251</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>83734</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>108132</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>68786</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>0.9294</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5405</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>5853</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>7313</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>11581</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>13110</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>17103</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>21916</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>0.9711</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>特定福祉用具販売</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>30299</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>37670</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>37720</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>50055</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>35272</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>61309</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>42720</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.9993</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>住宅改修</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>82735</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>88442</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>75695</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>82957</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>93788</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>61335</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>87106</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>1.004</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>99328</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>399801</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>1.1996</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>97944</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>65454</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>80834</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>148816</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>223992</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>288919</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>341950</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>313213</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>4715</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>14151</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>14698</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>17640</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>16788</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>17252</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>1.0556</v>
+      </c>
+    </row>
+    <row r="29" ht="62" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>注1）調整係数は「総括表詳細（４）の単価÷ツールの要介護度別単価を年報の利用者数で加重した平均」です。1.000から離れるほど、3町合計（ツール）と保険者単位（総括表）の水準の違いが大きい種別です。
+注2）要介護度別の内訳を持たない6種別（実績が0のもの）は掲げていません。
+注3）ツールは3町合計であり保険者単位ではありません。ここで用いるのは要介護度間の比（形）だけで、水準は総括表（保険者単位）に合わせています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2　令和11年度の要介護度別の給付費（円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>16,655,259</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>57,709,114</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>138,407,289</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>160,840,125</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>90,222,471</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>463,834,258</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>7,397,549</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>38,747,523</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>35,975,106</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>67,792,275</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>63,371,552</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>213,284,004</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>103,913,827</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>113,695,003</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>102,021,045</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>130,859,612</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>52,379,634</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>502,869,121</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>353,411</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>27,756,157</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>28,109,568</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>5,756,943</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>6,675,089</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>29,777,137</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>18,925,217</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>21,522,552</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>30,911,464</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>18,885,745</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>132,454,148</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>1,409,839</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>29,918,062</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>64,827,094</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>78,783,542</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>54,552,318</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>48,172,188</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>277,663,044</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>72,859,065</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>56,369,591</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>89,897,464</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>123,128,055</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>109,272,948</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>451,527,124</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>1,412,794</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>95,270</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>140,269</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>698,950</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>2,942,347</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>5,289,631</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>20,489,644</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>13,531,310</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>6,792,215</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>10,136,993</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>12,164,796</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>63,114,957</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>687,281</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>3,901,115</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>7,284,963</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>7,816,900</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>4,259,787</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>1,383,232</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>2,275,858</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>27,609,137</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>1,064,056</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>1,053,841</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>4,517,529</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>4,069,056</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>4,400,649</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>4,599,105</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>4,169,340</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>23,873,576</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>33,664,313</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>15,327,274</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>10,663,334</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>13,036,137</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>3,225,026</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>75,916,084</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>22,331,987</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>23,367,349</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>12,533,655</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>5,088,089</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>1,046,280</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>64,367,359</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>8,499,820</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>27,923,853</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>63,217,536</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>47,920,795</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>20,872,981</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>13,184,111</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>7,132,125</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>188,751,222</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>124,939</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>637,978</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>6,351,084</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>10,578,152</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>5,515,896</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>3,887,816</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>1,760,931</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>28,856,796</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>145,252</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>27,078</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>1,735,486</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>4,098,315</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>2,898,261</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>5,660,208</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>1,002,221</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>15,566,821</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>4,461,468</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>8,665,971</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>16,196,738</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>17,863,937</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>10,877,240</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>10,671,244</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>11,221,915</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>79,958,513</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>特定福祉用具販売</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>629,176</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>978,547</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>1,647,255</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>1,360,084</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>295,971</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>385,110</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>88,920</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>5,385,063</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>住宅改修</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>2,319,358</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>1,746,058</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>2,203,781</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>1,300,430</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>688,602</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>128,424</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>271,962</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>8,658,615</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>309,840</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>1,664,337</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>1,974,177</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>1,228,295</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>1,228,295</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>3,397,985</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>9,407,198</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>70,095,456</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>64,841,868</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>62,426,302</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>14,319,604</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>19,884,116</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>244,372,529</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>5,921,304</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>9,211,201</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>52,720,875</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>30,889,678</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>17,151,407</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>14,201,007</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>9,839,426</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>139,934,898</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="11" t="inlineStr"/>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>33,007,582</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>71,637,767</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>564,700,179</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>594,562,256</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>626,123,566</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>665,817,289</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>488,750,297</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>3,044,598,937</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>3　単価の構成の変化による差（単価ミックス効果）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>単価固定（06シート）</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>要介護度別の単価</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>差の率</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>2,978,267,893</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>2,978,975,041</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>707,147</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>+0.024％</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>3,010,470,894</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>3,011,540,164</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>1,069,271</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>+0.036％</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>3,043,161,657</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>3,044,598,937</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>1,437,280</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>+0.047％</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>3,310,122,835</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>3,317,848,527</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>7,725,692</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>+0.233％</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr"/>
+      <c r="H63" s="16" t="inlineStr"/>
+      <c r="I63" s="16" t="inlineStr"/>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>介護療養型医療施設</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>区域内に事業所なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>41.1％</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧。類型（混合型・介護専用型）は［要確認］</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>区域内に事業所なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>86.1％</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>99人＋［要確認］（東川町の1事業所が未確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="94" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>注1）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の在籍者とは数える対象が違います。調査②（施設調査）では特別養護老人ホーム等の在籍者146人に対し年報の受給者は197.5人／月であり、区域外の施設の利用が含まれます（調査結果と年報実績の突合 確認事項No.141）。したがって定員に対する率が100％を超えることがあります。
-注2）介護老人保健施設は令和7年度130人／月から令和8年度111人／月へ14.6％減少しています（確認事項No.133）。定員は平成27年度から3施設240人で不変です。本表は令和7年度を基準としており、この減少を将来へ延長していません。
-注3）特定施設入居者生活介護の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2　必要利用定員総数（日常生活圏域ごと）　据え置き案</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>日常生活圏域</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>サービス</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>現況（令和8年度）</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>東川町</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>36＋［要確認］（3）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>36＋［要確認］</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>36＋［要確認］</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>36＋［要確認］</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>東川町</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>0（0）</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>東川町</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>0（0）</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>27（2）</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>0（0）</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>42（2）</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>36（2）</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>0（0）</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>20（1）</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>99＋［要確認］（7）</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>99＋［要確認］</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>99＋［要確認］</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>99＋［要確認］</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>0（0）</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr"/>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>62（3）</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>第10期中の整備を見込まない（据え置き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="110" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>注1）これは据え置き案であり確定値ではありません。計画素案 第6章第4節4の本文は［要協議］のまま残しています。東川町は令和8年10月に施設整備・サービス提供方針を、東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しています（確認事項No.84・No.88）。
-注2）第10期中に整備の予定がない圏域は「0」と記載します。整備しないことも計画上の判断として記載するものです。
-注3）認知症対応型共同生活介護の定員は、北海道の名簿では7事業所108人、見える化システムD26（令和6年度）では5事業所99人であり一致しません。現に指定を受けている定員を3町への照会により確定する必要があります。
-注4）混合型特定施設入居者生活介護に係る必要利用定員総数を定めるかどうかは確認事項No.113です。特定施設の類型が未確認であるため定めていません。
-注5）区域内の施設の定員と保険者の受給者は一致しません（注1・1の表）。必要利用定員総数は区域内の施設の定員により定めるものであり、見込量（保険者の被保険者の受給）とは別に整理します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>3　令和9年4月新設のサービス区分</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>根拠</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>登録施設介護支援・登録施設介護予防支援</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>実績がないため0として立てる</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>特定地域サービス</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>実績がないため0として立てる</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>特定地域居宅サービス等事業</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>実績がないため0として立てる</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>注）見える化システムのサービス一覧には「登録施設介護支援」が既に現れています（全年度0.00％）。移行の範囲と単価が示されるまで見込量を0として立て、区分だけを掲げます（確認事項No.115）。夜間対応型訪問介護の区分もなお残っています。</t>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>3,408,932,536</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>3,418,469,468</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>9,536,931</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>+0.280％</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr"/>
+      <c r="H64" s="16" t="inlineStr"/>
+      <c r="I64" s="16" t="inlineStr"/>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="68" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>注1）06シートは種別ごとの単価（延べ1人あたり）を令和7年度で固定しています。要介護度別の単価を用いると、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
+注2）効きは第10期では小さく（令和11年度で+0.047％）、算定上の月額基準額で+2.2円です。令和22年度では+0.280％に開きます。
+注3）本表の採用値は06シート（単価固定）のままとしています。ツールの要介護度別の値は3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていないためです。［要確認］</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12112,38 +16839,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>地域支援事業の量と費用の見込み</t>
+          <t>在宅と施設の連鎖（見える化システムの構造との対照）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。令和7年度の実績が未受領であるため令和6年度の実績を基礎とします。</t>
+          <t>見える化システムは、認定者数から施設・居住系サービス利用者数を引いた残りを在宅サービスの分母に置きます（受領した参考シートからの逆算）。当方の算定は全サービスで認定者数を分母にしています。両者が一致することと、連鎖にする意味を示します。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>1　見える化システムの率の分母（実績値からの逆算）</t>
         </is>
       </c>
     </row>
@@ -12151,736 +16877,597 @@
       <c r="A5" s="4" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>率</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>単位</t>
+          <t>分母</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>R6実績
-（3町計）</t>
+          <t>逆算した分母</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
+          <t>参考となる値</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>延ばし方</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+          <t>確かめ方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>訪問型サービス（従前相当）　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>78.2</v>
-      </c>
+          <t>総括表詳細（２）　利用者数の割合</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>9123.2人</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>総括表の第1号被保険者数 9,119人</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+          <t>施設・居住系・在宅のどの行で逆算しても同じ値になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>通所型サービス（従前相当）　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>41.7</v>
-      </c>
+          <t>管理指標グラフ D32　受給率</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.1％＝約9.1人／月の刻み</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+          <t>小数第1位までの公表。小口のサービスには使えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>通所型サービスA　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>152.1</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>155.3</v>
-      </c>
+          <t>将来推計　在宅サービス利用率</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>認定者数−施設・居住系サービス利用者数</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1502.3人</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>当方の在宅の認定者数 1503.8人</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+          <t>月50人以上の10種別で逆算した中央値</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>通所型サービスC　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
+          <t>将来推計　施設・居住系サービス利用率</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>認定者数（推定）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>認定者数 1984人</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>在宅が残余であることと画面の設定順からの推定。［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R7 月平均（人）</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>画面の利用率</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>逆算した分母（人）</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>913.33</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>1493.6</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>642.08</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>1479.1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>1496.4</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1495.5</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>1518.1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>135.17</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>1506.9</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>1471.5</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>1513.7</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>1502.3</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>1531.3</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>注1）率は小数第4位までの公表であるため、月50人未満の種別では逆算した分母が大きく振れます。本表は月50人以上の種別に限っています。
+注2）逆算した分母の中央値1502.3人は、当方の在宅の認定者数（第1号認定者数1984人−施設・居住系480.2人＝1503.8人）に当たります。第1号被保険者数（9,119人）でも認定者数（1984人）でもありません。
+注3）**見込量を算定するための利用率の分母は認定者数です。**第1号被保険者数を分母に置くと、伸びが認定者数の伸びではなく第1号被保険者数の伸びに置き換わります。当方の推計では第1号被保険者数は令和7年度から令和11年度で＋1.36％、認定者数は＋4.21％であり、給付費が過小になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2　連鎖の形にした場合（在宅＝残余）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>R7実績</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>認定者数（人）</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>2025.1</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>2046.1</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2067.4</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>その他生活支援（配食）　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>その他生活支援（複合的提供）　利用者実人数</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>介護予防ケアマネジメントA　実施件数</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>件</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>199</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>203.1</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>205.2</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>介護予防ケアマネジメントC　実施件数</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>件</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の伸び</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>基本チェックリスト実施者数</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>243.5</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>244.4</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>245.3</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>第1号被保険者数の伸び</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績を据え置いて延ばす</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2　一般介護予防事業（通いの場）の量の見込み</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>単位</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>R6実績
-（3町計）</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>延ばし方</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系サービス利用者数（人／月）</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>480.2</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>在宅の認定者数（残余・人）</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>1503.8</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>1534.3</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>1549.9</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>1565.8</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　在宅の認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>通いの場　箇所数</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>箇所</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>据え置き</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績による</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>通いの場　参加者実人数</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>333.2</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>334.5</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>第1号被保険者数の伸び</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績による</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>通いの場　週1回以上の箇所数</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>箇所</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>据え置き</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度実績による</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数で延ばすものではありません。令和6年度の実績（25箇所）を据え置きました。目標値を置く場合は3町のご意向によります［要協議］。
-注2）参加者実人数の割合（第1号被保険者に対する）は代表KPI H05の指標です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>3　地域支援事業費の見込み（円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="4" t="inlineStr"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>R6実績</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>第10期計</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="D29" s="18" t="n">
+        <v>1.0203</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1.0307</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>1.0412</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸びとほぼ同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（参考）認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>介護予防・日常生活支援総合事業費</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>321,387,954</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>計画作成支援ツール（3町計）。令和7年度実績は未受領のため据え置き</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>包括的支援事業及び任意事業費</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>175,804,914</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費（保険料算定上のB）</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>177,161,259</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>177,161,259</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>177,161,259</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>177,161,259</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>531,483,777</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度決算（款4）から保険者機能強化推進事業費及び保険者努力支援事業費を除いたもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="68" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>注1）総合事業費は決算科目の「介護予防・生活支援サービス事業費」101,274,621円と5,854,697円の差があります。決算（広域連合の款項）と計画作成支援ツール（3町入力）で基礎が異なることによります。［要確認］
-注2）地域支援事業費（B）から2事業を除く方法を採っており、保険料収納必要額からの交付見込額の控除は行っていません。両者を併用すると二重控除になります（確認事項No.86）。控除する方法に改める場合はBを款4の全体183,384,259円に戻します。
-注3）令和7年度の総合事業の実績の提供を受けた時点で置き直します（資料提供依頼No.13）。</t>
+      <c r="D30" s="18" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1.0313</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1.0421</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>注1）利用率を令和7年度で固定し、認定者数が要介護度ごとに伸びる限り、1段（認定者数を分母にする）でも2段（在宅を残余にする）でも同じ結果になります。在宅の認定者数の伸びと認定者数の伸びの差は令和11年度で1.0412 と 1.0421 です。
+注2）**連鎖の形が要るのは、施設・居住系に定員上限を課す場合と、施設整備を施策として反映する場合です。**施設・居住系が頭打ちになれば、その分は在宅の認定者へ戻り、在宅サービスの見込量が増えます（10シート）。
+注3）当方の算定は1段のままとしています。10シートで定員上限を課した場合の振替を別に示します。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -2188,7 +2188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
     <row r="11" ht="104" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達します。**令和17年度には定員を超えます。介護老人福祉施設も令和22年度に定員を超えます。
+          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達します。**中長期の年次を令和12・27・32年度まで広げたところ（令和8年9月24日。確認事項No.157）、**定員を超えるのは令和17年度ではなく令和12年度**であることが分かりました。従前は令和12年度を算定していなかったため令和17年度としていました。介護老人福祉施設は令和22年度に定員を超えます。
 注2）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の定員は当連合の被保険者にとっての上限ではなく、区域外の施設の利用により定員を超える受給が生じ得ます（確認事項No.141）。したがって到達率が100％を超えることは誤りではありません。ただし区域内で受け止めるのであれば整備を要します。
 注3）介護老人保健施設（58.4％）・特定施設入居者生活介護（41.1％）は定員に余裕があります。特定施設の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］
 注4）認知症対応型共同生活介護の定員は99人＋［要確認］です。東川町の1事業所の定員が未確定であるため、到達率は上側に振れています。</t>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>547.2</v>
+        <v>505.6</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>541.6</v>
+        <v>505.2</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>1680.7</v>
+        <v>1577.5</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>1686.3</v>
+        <v>1577.9</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>+0.33％</t>
+          <t>+0.03％</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -2647,37 +2647,142 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>541.6</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>1680.7</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1686.3</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>+0.33％</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>超過分が在宅へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C20" s="15" t="n">
         <v>563.9</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D20" s="28" t="n">
         <v>10.8</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E20" s="15" t="n">
         <v>553.1</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F20" s="15" t="n">
         <v>1724.2</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G20" s="15" t="n">
         <v>1735</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>+0.63％</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>超過分が在宅へ戻る</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>538.4</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1657.6</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>1662.1</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>+0.27％</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>超過分が在宅へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>535.2</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>1654.7</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>1658.8</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>+0.25％</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>超過分が在宅へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>注1）第10期（令和9〜11年度）では超過が生じません。定員上限を課しても見込量は動きません。
 注2）令和22年度では10.8人が超過し、在宅の認定者数が0.63％増えます。中長期の見込みでは供給の制約が効きはじめます。
@@ -2686,123 +2791,48 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>3　供給の制約のうち反映していないもの</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>制約</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>人材</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>介護職員・看護職員の確保の見通し。見える化M系列の従業員総数はあるが、将来の確保可能量は調査していない</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>反映していない（確認事項No.116）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>受入可能量</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>定員があっても、職員の不足により実際には受け入れられない床がある。事業所への意向調査を行っていない</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>反映していない。定員をそのまま上限としている</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>休止・廃止の意向</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>事業所の休止・廃止・縮小の意向を把握していない</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>反映していない</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>区域外の施設の受入れ</t>
+          <t>人材</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>当連合の被保険者の区域外利用は年報に含まれるが、区域外の施設に受け入れる余力があるかは分からない</t>
+          <t>介護職員・看護職員の確保の見通し。見える化M系列の従業員総数はあるが、将来の確保可能量は調査していない</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -2812,22 +2842,22 @@
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>現状の利用の続くことを前提としている</t>
+          <t>反映していない（確認事項No.116）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>住所地特例</t>
+          <t>受入可能量</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>年報様式1で77人と分かるが、住所地特例に当たらない区域外利用は分けられない</t>
+          <t>定員があっても、職員の不足により実際には受け入れられない床がある。事業所への意向調査を行っていない</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2837,19 +2867,94 @@
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="6" t="inlineStr">
         <is>
+          <t>反映していない。定員をそのまま上限としている</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>休止・廃止の意向</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>事業所の休止・廃止・縮小の意向を把握していない</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>反映していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>区域外の施設の受入れ</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>当連合の被保険者の区域外利用は年報に含まれるが、区域外の施設に受け入れる余力があるかは分からない</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>現状の利用の続くことを前提としている</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>住所地特例</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>年報様式1で77人と分かるが、住所地特例に当たらない区域外利用は分けられない</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
           <t>分けずに算定している（確認事項No.141）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3641,31 +3746,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中長期推計（令和17年度・令和22年度）</t>
+          <t>中長期推計（令和12年度・令和17年度・令和22年度・令和27年度・令和32年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>改正法により令和22年度（2040年）を含む中長期の見込みが記載事項となります（確認事項No.114）。従前は認定者数までしか算定していませんでした。</t>
+          <t>改正法により令和22年度（2040年）を含む中長期の見込みが記載事項となります（確認事項No.114）。従前は認定者数までしか算定していませんでした。見える化システムは令和12・27・32年度も求めるため、令和8年9月24日に5年次へ広げました（確認事項No.157）。計画本文に掲げるのは従前どおり令和17年度・令和22年度です。</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3802,31 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>置き方</t>
         </is>
@@ -3727,14 +3848,22 @@
         <v>9213.4</v>
       </c>
       <c r="E6" s="15" t="n">
+        <v>9211.4</v>
+      </c>
+      <c r="F6" s="15" t="n">
         <v>9249.9</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="G6" s="15" t="n">
         <v>9491.299999999999</v>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="H6" s="15" t="n">
+        <v>9395</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>9127.1</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>案C。令和12年度以降は令和11年度を起点に社人研推計の伸び率で接続</t>
         </is>
@@ -3756,14 +3885,22 @@
         <v>2067.4</v>
       </c>
       <c r="E7" s="15" t="n">
+        <v>2083.1</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <v>2227.9</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="15" t="n">
         <v>2288.2</v>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="H7" s="15" t="n">
+        <v>2196</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>2189.9</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>シナリオ②。令和11年度以降は認定率を固定</t>
         </is>
@@ -3785,14 +3922,22 @@
         <v>22.4</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>24.1</v>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="G8" s="15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>認定者数÷第1号</t>
         </is>
@@ -3824,21 +3969,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>R22／R7</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>R32／R7</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -3860,16 +4019,24 @@
         <v>352.3</v>
       </c>
       <c r="E12" s="15" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>384.8</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="G12" s="15" t="n">
         <v>396.7</v>
       </c>
-      <c r="G12" s="19" t="n">
-        <v>1.177</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="H12" s="15" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -3887,16 +4054,24 @@
         <v>149.4</v>
       </c>
       <c r="E13" s="15" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>162.4</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="G13" s="15" t="n">
         <v>167.2</v>
       </c>
-      <c r="G13" s="19" t="n">
-        <v>1.169</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="H13" s="15" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>159</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -3914,16 +4089,24 @@
         <v>2956.6</v>
       </c>
       <c r="E14" s="15" t="n">
+        <v>2978.9</v>
+      </c>
+      <c r="F14" s="15" t="n">
         <v>3194.5</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="G14" s="15" t="n">
         <v>3284</v>
       </c>
-      <c r="G14" s="19" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="H14" s="15" t="n">
+        <v>3148.2</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>3135.7</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="11" t="inlineStr"/>
@@ -3939,16 +4122,24 @@
         <v>3458.3</v>
       </c>
       <c r="E15" s="20" t="n">
+        <v>3484.5</v>
+      </c>
+      <c r="F15" s="20" t="n">
         <v>3741.8</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="G15" s="20" t="n">
         <v>3847.9</v>
       </c>
-      <c r="G15" s="21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="H15" s="20" t="n">
+        <v>3686.6</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>3670.9</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="4" t="inlineStr"/>
@@ -3969,21 +4160,35 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>令和12年度（円）</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>令和17年度（円）</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>令和22年度（円）</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>R22／R7</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度（円）</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度（円）</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>R32／R7</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -4008,19 +4213,33 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
+          <t>3,066,588,037</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
           <t>3,310,122,835</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>3,408,932,536</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n">
-        <v>1.169</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>単価は令和7年度で固定</t>
         </is>
@@ -4107,23 +4326,23 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,066,588,037</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9250</v>
+        <v>9211</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>6988</v>
+        <v>6527</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+49</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -4140,23 +4359,23 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>令和22年度</t>
+          <t>令和17年度</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>3,408,932,536</t>
+          <t>3,310,122,835</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>9491</v>
+        <v>9250</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>7003</v>
+        <v>6988</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>+525</t>
+          <t>+510</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -4167,24 +4386,124 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>3,408,932,536</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>9491</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>7003</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>+525</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費・総合事業費は令和6年度水準で据え置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>9395</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>6779</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費・総合事業費は令和6年度水準で据え置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>9127</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>6940</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+462</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費・総合事業費は令和6年度水準で据え置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="92" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>注1）中長期の月額は、その年度の給付費の水準が3年続いたと置いて第10期と同じ式で計算した参考値です。第11期以降の保険料を算定したものではありません。
 注2）単価（1人あたり給付費）を令和7年度で固定しているため、報酬改定と単価の趨勢（年率1.75％）は入っていません。令和22年度までの13年間で単価が年1.75％で伸びれば給付費は約1.25倍になります。
 注3）第1号被保険者数は令和7年度9,090人から令和22年度9,491人へ4.4％減少し、認定者数は1,984人から2,288人へ15.3％増加します。保険料の分母が縮み分子が伸びる形になります。
-注4）地域支援事業費・総合事業費・第1号被保険者負担割合・予定収納率はいずれも令和6年度又は第9期の水準で据え置いています。</t>
+注4）地域支援事業費・総合事業費・第1号被保険者負担割合・予定収納率はいずれも令和6年度又は第9期の水準で据え置いています。
+注5）令和12・27・32年度は見える化システムが求めるため算定したものです（確認事項No.157）。計画本文に掲げるのは令和17年度・令和22年度です。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6542,7 +6861,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>29サービス×5年度</t>
+          <t>29サービス×8年度</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -7768,7 +8087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8162,276 +8481,462 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>324.9</v>
+        <v>311.7</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>319.1</v>
+        <v>305.7</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>579.1</v>
+        <v>539.2</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>340.6</v>
+        <v>314.9</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>245.3</v>
+        <v>224.2</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>243.9</v>
+        <v>224.8</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>175</v>
+        <v>162.5</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>2227.9</v>
+        <v>2083.1</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>579.1</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>245.3</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>243.9</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>2227.9</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B20" s="17" t="n">
         <v>331</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C20" s="17" t="n">
         <v>325</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D20" s="17" t="n">
         <v>596.4</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E20" s="17" t="n">
         <v>350.9</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F20" s="17" t="n">
         <v>253.3</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G20" s="17" t="n">
         <v>251.3</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H20" s="17" t="n">
         <v>180.3</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I20" s="17" t="n">
         <v>2288.2</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>239.7</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>567</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>238.6</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>2189.9</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>3　令和7年度に対する伸び（倍）</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>要支援1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>要支援2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>要介護1</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>要介護2</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>要介護3</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>要介護4</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>要介護5</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>一律（総数）</t>
         </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n">
-        <v>1.0189</v>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1.0193</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1.0196</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1.0222</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1.0241</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>1.0231</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>1.0207</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n">
-        <v>1.0285</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>1.0291</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1.0296</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1.0335</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1.0364</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>1.0349</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>1.0303</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>1.0313</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>1.0383</v>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>1.0391</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>1.0398</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>1.0451</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>1.0489</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>1.0469</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>1.0407</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>1.0421</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和9年度</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>1.0904</v>
+        <v>1.0189</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1.0928</v>
+        <v>1.0193</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1.1244</v>
+        <v>1.0196</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1.1392</v>
+        <v>1.0222</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1.157</v>
+        <v>1.0241</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>1.1451</v>
+        <v>1.0231</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>1.1287</v>
+        <v>1.02</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>1.1229</v>
+        <v>1.0207</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1.0291</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1.0296</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1.0335</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>1.0349</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1.0303</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>1.0313</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>1.0383</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>1.0391</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>1.0398</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>1.0451</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>1.0489</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>1.0469</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>1.0407</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>1.0421</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>1.0469</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1.0471</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1.0533</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>1.0577</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>1.0555</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>1.0481</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>1.0499</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>1.0904</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>1.0928</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1.1244</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1.1392</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>1.1451</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>1.1287</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>1.1229</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B31" s="18" t="n">
         <v>1.1106</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C31" s="18" t="n">
         <v>1.1131</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D31" s="18" t="n">
         <v>1.158</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E31" s="18" t="n">
         <v>1.1734</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F31" s="18" t="n">
         <v>1.1948</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G31" s="18" t="n">
         <v>1.1799</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H31" s="18" t="n">
         <v>1.1632</v>
       </c>
-      <c r="I27" s="18" t="n">
+      <c r="I31" s="18" t="n">
         <v>1.1533</v>
       </c>
     </row>
-    <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1.0777</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1.0795</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1.1098</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1.1207</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>1.1356</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>1.1253</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>1.1133</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>1.1069</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1.0871</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1.1009</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1.1148</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1.1277</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>1.1041</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>1.1038</v>
+      </c>
+    </row>
+    <row r="34" ht="76" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>注1）要介護度別の伸びは一律ではありません。85歳以上の人口が増えることにより、85歳以上に多い要介護度の伸びが総数の伸びを上回ります。令和11年度で最も高いのは要介護3の1.0489、最も低いのは要支援1の1.0383です。
 注2）要介護度の構成そのもの（同じ年齢階級の中での構成）は令和7年度末の実績で固定しています。認知症の人の増加や医療の変化による構成の変化は反映していません（15シート）。
@@ -8443,11 +8948,11 @@
   <mergeCells count="7">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14383,7 +14888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16740,27 +17245,27 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,066,588,037</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>3,317,848,527</t>
+          <t>3,068,203,871</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>7,725,692</t>
+          <t>1,615,834</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>+0.233％</t>
+          <t>+0.053％</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr"/>
@@ -16778,27 +17283,27 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>令和22年度</t>
+          <t>令和17年度</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>3,408,932,536</t>
+          <t>3,310,122,835</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>3,418,469,468</t>
+          <t>3,317,848,527</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>9,536,931</t>
+          <t>7,725,692</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>+0.280％</t>
+          <t>+0.233％</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr"/>
@@ -16810,8 +17315,122 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="68" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>3,408,932,536</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>3,418,469,468</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>9,536,931</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>+0.280％</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr"/>
+      <c r="H65" s="16" t="inlineStr"/>
+      <c r="I65" s="16" t="inlineStr"/>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>3,265,402,536</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>6,577,487</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>+0.202％</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr"/>
+      <c r="H66" s="16" t="inlineStr"/>
+      <c r="I66" s="16" t="inlineStr"/>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>3,245,610,859</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>5,275,646</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>+0.163％</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr"/>
+      <c r="H67" s="16" t="inlineStr"/>
+      <c r="I67" s="16" t="inlineStr"/>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>要介護度の重い方の割合が増えるため単価の平均が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="68" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>注1）06シートは種別ごとの単価（延べ1人あたり）を令和7年度で固定しています。要介護度別の単価を用いると、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
 注2）効きは第10期では小さく（令和11年度で+0.047％）、算定上の月額基準額で+2.2円です。令和22年度では+0.280％に開きます。
@@ -16826,8 +17445,8 @@
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A65:J65"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A68:J68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -2444,7 +2444,7 @@
     <row r="11" ht="104" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達します。**中長期の年次を令和12・27・32年度まで広げたところ（令和8年9月24日。確認事項No.157）、**定員を超えるのは令和17年度ではなく令和12年度**であることが分かりました。従前は令和12年度を算定していなかったため令和17年度としていました。介護老人福祉施設は令和22年度に定員を超えます。
+          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する見込みです。**中長期の年次を令和12・27・32年度まで広げたところ（令和8年9月24日。確認事項No.157）、**定員を超えるのは令和17年度ではなく令和12年度**であることが分かりました。従前は令和12年度を算定していなかったため令和17年度としていました。介護老人福祉施設は令和22年度に定員を超えます。
 注2）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の定員は当連合の被保険者にとっての上限ではなく、区域外の施設の利用により定員を超える受給が生じ得ます（確認事項No.141）。したがって到達率が100％を超えることは誤りではありません。ただし区域内で受け止めるのであれば整備を要します。
 注3）介護老人保健施設（58.4％）・特定施設入居者生活介護（41.1％）は定員に余裕があります。特定施設の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］
 注4）認知症対応型共同生活介護の定員は99人＋［要確認］です。東川町の1事業所の定員が未確定であるため、到達率は上側に振れています。</t>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護が令和11年度に定員に達することへの対応</t>
+          <t>地域密着型介護老人福祉施設入所者生活介護が令和11年度に定員に達する見込みであることへの対応</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>本表の見込みでは令和11年度に61.9人／月となり、区域内の定員62人の99.9％に達します。令和17年度には超えます。①区域外の施設の利用で受け止めるか、②整備するか、③見込量の側を定員で頭打ちにするかのご協議をお願いします。年報は施設の所在地を問わず当連合の被保険者を数えるため、区域内の定員は上限ではありません（確認事項No.141）。本表は頭打ちを課していません（第10期は差が生じません）。</t>
+          <t>本表の見込みでは令和11年度に61.9人／月となり、区域内の定員62人の99.9％に達する見込みです。令和12年度には超えると見込まれます。①区域外の施設の利用で受け止めるか、②整備するか、③見込量の側を定員で頭打ちにするかのご協議をお願いします。年報は施設の所在地を問わず当連合の被保険者を数えるため、区域内の定員は上限ではありません（確認事項No.141）。本表は頭打ちを課していません（第10期は差が生じません）。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -121,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,11 +143,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,6 +273,8 @@
     <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -736,7 +782,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。総合事業の令和7年度実績が未受領であるため、令和6年度の実施状況調査の実績を据え置いて量を置きました。</t>
+          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。令和7年度の実施状況は3町の実施報告書により確認できましたが、量の単位が延べ人数であり国の調査の利用者実人数とは数えているものが違うため、令和6年度の実施状況調査の実績を据え置いて量を置きました。</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -2444,7 +2490,7 @@
     <row r="11" ht="104" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>注1）**地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する見込みです。**中長期の年次を令和12・27・32年度まで広げたところ（令和8年9月24日。確認事項No.157）、**定員を超えるのは令和17年度ではなく令和12年度**であることが分かりました。従前は令和12年度を算定していなかったため令和17年度としていました。介護老人福祉施設は令和22年度に定員を超えます。
+          <t>注1）地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する見込みです。中長期の年次を令和12・27・32年度まで広げたところ（令和8年9月24日。確認事項No.157）、定員を超えるのは令和17年度ではなく令和12年度であることが分かりました。従前は令和12年度を算定していなかったため令和17年度としていました。介護老人福祉施設は令和22年度に定員を超えます。
 注2）年報は施設の所在地を問わず当連合の被保険者を数えます。区域内の施設の定員は当連合の被保険者にとっての上限ではなく、区域外の施設の利用により定員を超える受給が生じ得ます（確認事項No.141）。したがって到達率が100％を超えることは誤りではありません。ただし区域内で受け止めるのであれば整備を要します。
 注3）介護老人保健施設（58.4％）・特定施設入居者生活介護（41.1％）は定員に余裕があります。特定施設の率が低いのは、入居者に要支援の方が含まれ介護予防特定施設入居者生活介護として計上されるためとみられます。［要確認］
 注4）認知症対応型共同生活介護の定員は99人＋［要確認］です。東川町の1事業所の定員が未確定であるため、到達率は上側に振れています。</t>
@@ -2787,7 +2833,7 @@
           <t>注1）第10期（令和9〜11年度）では超過が生じません。定員上限を課しても見込量は動きません。
 注2）令和22年度では10.8人が超過し、在宅の認定者数が0.63％増えます。中長期の見込みでは供給の制約が効きはじめます。
 注3）在宅へ戻った分がどのサービスへ向かうかは、在宅サービスの利用率を掛けて配分することになります。本表はその配分を行っていません。施設に入れない方の在宅サービスの使い方が在宅の平均と同じであるとは限らないためです。［要協議］
-注4）**本表の採用値は頭打ちを課さないものとしています。**第10期では差がなく、また区域外の施設の利用により定員を超える受給が生じ得るためです。</t>
+注4）本表の採用値は頭打ちを課さないものとしています。第10期では差がなく、また区域外の施設の利用により定員を超える受給が生じ得るためです。</t>
         </is>
       </c>
     </row>
@@ -2966,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2990,7 +3036,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。令和7年度の実績が未受領であるため令和6年度の実績を基礎とします。</t>
+          <t>法第117条第2項第2号の基本的記載事項でありながら、計画素案は費用の額のみで量がありません（確認事項No.112）。令和7年度の実施状況は3町の実施報告書により確認できましたが、量の単位が延べ人数であるため、見込みの基礎は令和6年度の利用者実人数のままとします。</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3597,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3　地域支援事業費の見込み（円）</t>
+          <t>3　令和7年度の実施状況（3町の実施報告書による）</t>
         </is>
       </c>
     </row>
@@ -3559,33 +3605,25 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>R6実績</t>
-        </is>
-      </c>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>事業区分</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
+          <t>量（原文）</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>第10期計</t>
+          <t>単位</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -3594,146 +3632,553 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業費</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護相当サービス</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="n"/>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>107,129,318</t>
-        </is>
-      </c>
+          <t>332人（延）</t>
+        </is>
+      </c>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="29" t="n"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>321,387,954</t>
+          <t>延べ人数</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツール（3町計）。令和7年度実績は未受領のため据え置き</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
+          <t>東神楽町ホームヘルプサービスセンター、他事業所</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>包括的支援事業及び任意事業費</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>通所介護相当サービス</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="n"/>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>58,601,638</t>
-        </is>
-      </c>
+          <t>375人（延）</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="29" t="n"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>175,804,914</t>
+          <t>延べ人数</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
+          <t>東神楽町デイサービスセンター、他事業所</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスＡ（緩和した基準によるサービス）</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>年143日／延べ1,173名</t>
+        </is>
+      </c>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスA／（はれのひ：R7.6～開所）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスＡ（緩和した基準によるサービス）</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>延1,197人</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="29" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>慈光園通所型サービスＡ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスＡ（緩和した基準によるサービス）</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>延344人</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="29" t="n"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>生きがいデイサービス事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスＡ（緩和した基準によるサービス）</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>465人（延）</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町高齢者基準緩和型通所サービス（あえるday）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスＣ（短期集中予防サービス）</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>延0人</t>
+        </is>
+      </c>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>慈光園通所型サービスＣ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>栄養改善を目的とした配食</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>4,298人（延）</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町配食サービス事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>訪問型サービス・通所型サービスの一体的提供等</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>延173人</t>
+        </is>
+      </c>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="29" t="n"/>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>生活支援サービス（小規模多機能七彩、虹、燈、ひなた、ほたる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>（４）介護予防ケアマネジメント（第１号介護予防支援事業）</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>1,035人（延）</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>延べ人数</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>東神楽地域包括支援センター、他委託居宅支援事業所</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>注1）3町の実施報告書（令和8年9月25日受領）による令和7年度の実績です。記載のある事業のみを掲げています。
+注2）単位が延べ人数・食数・回数で混在するため、1の表（利用者実人数）に置き換えることはできません。3町を足して広域連合の量とすることもできません。
+注3）東川町・美瑛町は訪問介護相当・通所介護相当の量の記載がなく、3町がそろう事業区分は通所型サービスＡのみです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>4　地域支援事業費の見込み（円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>R6実績</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>第10期計</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>107,129,318</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>321,387,954</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール（3町計）。令和7年度実績は未受領のため据え置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業及び任意事業費</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>58,601,638</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>175,804,914</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>地域支援事業費（保険料算定上のB）</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>177,161,259</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>177,161,259</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>177,161,259</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>177,161,259</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>531,483,777</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>令和6年度決算（款4）から保険者機能強化推進事業費及び保険者努力支援事業費を除いたもの</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="68" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="42" ht="68" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>注1）総合事業費は決算科目の「介護予防・生活支援サービス事業費」101,274,621円と5,854,697円の差があります。決算（広域連合の款項）と計画作成支援ツール（3町入力）で基礎が異なることによります。［要確認］
 注2）地域支援事業費（B）から2事業を除く方法を採っており、保険料収納必要額からの交付見込額の控除は行っていません。両者を併用すると二重控除になります（確認事項No.86）。控除する方法に改める場合はBを款4の全体183,384,259円に戻します。
-注3）令和7年度の総合事業の実績の提供を受けた時点で置き直します（資料提供依頼No.13）。</t>
+注3）令和7年度の事業ごとの利用者実人数の提供を受けた時点で置き直します（資料提供依頼No.13）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="29">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E33:G33"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E29:G29"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5460,7 +5905,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="31" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5483,10 +5928,10 @@
           <t>3,043,161,657</t>
         </is>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="31" t="n">
         <v>9031.9</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="31" t="n">
         <v>6436</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -5607,7 +6052,7 @@
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>注1）改定率1％あたり月額+61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
-注2）**改定は令和9年度の1回だけを見ています。**第10期中の改定は令和9年度のみです（次は令和12年度）。
+注2）改定は令和9年度の1回だけを見ています。第10期中の改定は令和9年度のみです（次は令和12年度）。
 注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
 注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
         </is>
@@ -6005,12 +6450,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の総合事業の実績</t>
+          <t>令和7年度の総合事業の事業費</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>未受領である（資料提供依頼No.13）</t>
+          <t>3町の実施報告書（令和8年9月25日受領）に費用の額の記載がない</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -6040,12 +6485,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>事業ごとの利用者実人数（令和7年度）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>同上。令和6年度の実施状況調査は受領済みである</t>
+          <t>3町の実施報告書により実施状況は確認できたが、量の単位が延べ人数であり実人数ではない</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
@@ -7318,12 +7763,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位の給付費の差（令和7年度4.0％）</t>
+          <t>給付費データの給付費総額と年報の給付費の範囲の違い</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.87として照会中です。本表は広域連合単位（年報）によります</t>
+          <t>給付費総額は保険請求額と保険利用者負担額の合計であり費用額に当たります。本表は年報及び総括表（保険給付費）によります</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -7604,12 +8049,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の令和7年度実績</t>
+          <t>介護予防・日常生活支援総合事業の事業ごとの利用者実人数（令和7年度）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13のうち未受領の部分です。本表11シートは令和6年度の実施状況調査を据え置いています。令和7年度の実績により置き直します。</t>
+          <t>令和8年9月25日に3町の実施報告書を受領し、実施状況と量を確認できました。ただし量の単位が延べ人数であり、令和6年度の実施状況調査の利用者実人数に置き換えられません。事業ごとの利用者実人数と事業費のご提供をお願いします。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -8034,7 +8479,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>市町村Ⅲ（サービス・活動事業等）・市町村Ⅱ（一般介護予防事業）</t>
+          <t>市町村Ⅲ（サービス・活動事業等）・市町村Ⅱ（一般介護予防事業）。令和7年度の実施状況は3町の実施報告書により別に掲げる</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8512,7 @@
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>注1）年報は保険者（広域連合）単位であり、介護保険事業計画作成支援ツールの3町合計とは範囲が異なります。同じ令和7年度の施設・居住系の月平均利用者数でツール527人に対し年報480.17人（＋9.8％）の開きがあります（確認事項No.145）。保険料は保険者単位で算定するため年報によります。
-注2）令和7年度の給付費は3町合計と広域連合単位に129,580,267円（4.0％）の差があります（確認事項No.87）。令和6年度・令和8年度は完全に一致します。</t>
+注2）給付費データの3町のファイルの合計と広域連合単位のファイルは、令和6年度から令和8年度まで円単位で一致します（確認事項No.87は解決しました）。</t>
         </is>
       </c>
     </row>
@@ -17905,7 +18350,7 @@
         <is>
           <t>注1）率は小数第4位までの公表であるため、月50人未満の種別では逆算した分母が大きく振れます。本表は月50人以上の種別に限っています。
 注2）逆算した分母の中央値1502.3人は、当方の在宅の認定者数（第1号認定者数1984人−施設・居住系480.2人＝1503.8人）に当たります。第1号被保険者数（9,119人）でも認定者数（1984人）でもありません。
-注3）**見込量を算定するための利用率の分母は認定者数です。**第1号被保険者数を分母に置くと、伸びが認定者数の伸びではなく第1号被保険者数の伸びに置き換わります。当方の推計では第1号被保険者数は令和7年度から令和11年度で＋1.36％、認定者数は＋4.21％であり、給付費が過小になります。</t>
+注3）見込量を算定するための利用率の分母は認定者数です。第1号被保険者数を分母に置くと、伸びが認定者数の伸びではなく第1号被保険者数の伸びに置き換わります。当方の推計では第1号被保険者数は令和7年度から令和11年度で＋1.36％、認定者数は＋4.21％であり、給付費が過小になります。</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18519,7 @@
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>注1）利用率を令和7年度で固定し、認定者数が要介護度ごとに伸びる限り、1段（認定者数を分母にする）でも2段（在宅を残余にする）でも同じ結果になります。在宅の認定者数の伸びと認定者数の伸びの差は令和11年度で1.0412 と 1.0421 です。
-注2）**連鎖の形が要るのは、施設・居住系に定員上限を課す場合と、施設整備を施策として反映する場合です。**施設・居住系が頭打ちになれば、その分は在宅の認定者へ戻り、在宅サービスの見込量が増えます（10シート）。
+注2）連鎖の形が要るのは、施設・居住系に定員上限を課す場合と、施設整備を施策として反映する場合です。施設・居住系が頭打ちになれば、その分は在宅の認定者へ戻り、在宅サービスの見込量が増えます（10シート）。
 注3）当方の算定は1段のままとしています。10シートで定員上限を課した場合の振替を別に示します。</t>
         </is>
       </c>

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -5855,7 +5855,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和9年度は介護報酬改定の年に当たります（3年周期）。改定率が未公表であるため単価を令和7年度で固定していますが、改定率を一律に乗じた場合に月額がどこまで動くかを示します。</t>
+          <t>令和9年度は介護報酬改定の年に当たります（3年周期）。加えて、令和9年度改定を待たずに令和8年度にも改定が行われることが令和8年3月の全国課長会議資料に示されています。いずれも改定率が未公表であるため単価を令和7年度で固定していますが、改定率を一律に乗じた場合に月額がどこまで動くかを示します。</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>注1）改定率1％あたり月額+61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
-注2）改定は令和9年度の1回だけを見ています。第10期中の改定は令和9年度のみです（次は令和12年度）。
+注2）本表の改定率は1回分の改定を見たものです。第10期の期間中の改定は令和9年度のみです（次は令和12年度）が、基準年度である令和7年度の単価には令和8年度改定も反映されていないため、令和7年度の単価から見れば2回分の改定が織り込まれていません。2回分を織り込む場合は、本表の改定率を2回分の合計として読みます。
 注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
 注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
         </is>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>令和9年度は報酬改定の年に当たるが改定率は未公表である</t>
+          <t>令和9年度は報酬改定の年に当たるが改定率は未公表である。加えて令和8年度にも改定が行われるため、令和7年度の単価は2回分の改定を織り込んでいない</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -1072,12 +1072,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>9,031,900,444円</t>
+          <t>9,035,114,142円</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
     </row>
@@ -4653,36 +4653,36 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>3,066,588,037</t>
+          <t>3,068,203,871</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,317,848,527</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>3,408,932,536</t>
+          <t>3,418,469,468</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>3,258,825,048</t>
+          <t>3,265,402,536</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>3,240,335,214</t>
+          <t>3,245,610,859</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
-        <v>1.111</v>
+        <v>1.113</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>9213</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>6478</v>
+        <v>6481</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>3,066,588,037</t>
+          <t>3,068,203,871</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>9211</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>6527</v>
+        <v>6530</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
@@ -4809,18 +4809,18 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,317,848,527</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>9250</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>6988</v>
+        <v>7003</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+522</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -4842,18 +4842,18 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>3,408,932,536</t>
+          <t>3,418,469,468</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>9491</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>7003</v>
+        <v>7022</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>+525</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -4875,18 +4875,18 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>3,258,825,048</t>
+          <t>3,265,402,536</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>9395</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>6779</v>
+        <v>6792</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>+300</t>
+          <t>+311</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -4908,18 +4908,18 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>3,240,335,214</t>
+          <t>3,245,610,859</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>9127</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>6940</v>
+        <v>6951</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>+462</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9,031,900,444</t>
+          <t>9,035,114,142</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>11,671,563</t>
+          <t>14,885,261</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>9,565,616,321</t>
+          <t>9,569,019,924</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>12,361,263</t>
+          <t>15,764,866</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>10,097,100,098</t>
+          <t>10,100,503,701</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>12,361,263</t>
+          <t>15,764,866</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>9,887,004,275</t>
+          <t>9,890,407,878</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>12,361,263</t>
+          <t>15,764,866</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2,322,333,022</t>
+          <t>2,323,115,851</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2,843,090</t>
+          <t>3,625,919</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>494,350,214</t>
+          <t>494,520,394</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>618,063</t>
+          <t>788,243</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>729,213,412</t>
+          <t>729,464,444</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>911,702</t>
+          <t>1,162,734</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824</t>
+          <t>2,088,171,801</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>2,549,452</t>
+          <t>3,251,429</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>+8円</t>
+          <t>+10円</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -5542,22 +5542,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>9,031,900,444</t>
+          <t>9,035,114,142</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5672,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>9,565,616,321</t>
+          <t>9,569,019,924</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>46,404,797（+0.5％）</t>
+          <t>49,808,400（+0.5％）</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824</t>
+          <t>2,088,171,801</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>35,501,357（+1.7％）</t>
+          <t>36,203,334（+1.8％）</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>+8円（+0.1％）</t>
+          <t>+10円（+0.2％）</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
@@ -5915,24 +5915,24 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="F6" s="31" t="n">
-        <v>9031.9</v>
+        <v>9035.1</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>6436</v>
+        <v>6438</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -5951,24 +5951,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3,008,050,572</t>
+          <t>3,008,764,791</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>3,040,575,602</t>
+          <t>3,041,655,566</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>3,073,593,274</t>
+          <t>3,075,044,927</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>9122.200000000001</v>
+        <v>9125.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>6497</v>
+        <v>6499</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -5987,24 +5987,24 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3,037,833,251</t>
+          <t>3,038,554,541</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>3,070,680,311</t>
+          <t>3,071,770,968</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>3,104,024,890</t>
+          <t>3,105,490,916</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9212.5</v>
+        <v>9215.799999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6558</v>
+        <v>6560</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -6023,28 +6023,28 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>3,067,615,930</t>
+          <t>3,068,344,292</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>3,100,785,020</t>
+          <t>3,101,886,369</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>3,134,456,507</t>
+          <t>3,135,936,905</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>9302.9</v>
+        <v>9306.200000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6619</v>
+        <v>6621</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>+182円</t>
+          <t>+183円</t>
         </is>
       </c>
     </row>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9031.9</v>
+        <v>9035.1</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6436</v>
+        <v>6438</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9348</v>
+        <v>9351.299999999999</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6649</v>
+        <v>6651</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -6161,14 +6161,14 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>9516.6</v>
+        <v>9520</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6762</v>
+        <v>6765</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>+326円</t>
+          <t>+327円</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（４）は要介護度別の内訳を持たない。計画作成支援ツールは要介護度別を持つが3町合計である</t>
+          <t>総括表詳細（４）は要介護度別の内訳を持たない。要介護度間の比は給付費データ（保険者単位）から採れる（従前「計画作成支援ツールは3町合計であり比が保険者単位でも同じかは未確認」としていたのは当たらない）</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>ツールから要介護度間の比（形）だけを採り、水準は総括表に合わせて比例調整した。採用値は単価固定（06シート）のままとし、07シートに別掲した</t>
+          <t>**令和8年10月1日に採用し、据え置きを解消した。**要介護度間の比を給付費データ（保険者単位）から採り、水準は総括表に合わせて比例調整している。基準年度では総括表の給付費を円単位で再現する（点検16）</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の単価を用いると令和11年度＋0.047％（月額＋2円）、令和22年度＋0.280％</t>
+          <t>採用により総給付費（3か年）＋3,213,698円・月額＋2.17円。保険料基準額は6,400円で変わらない</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>同上。回数の趨勢は年率＋0.25％（中央値）にとどまる</t>
+          <t>年報の要介護度別の明細により要介護度別に求められる（見える化システムの画面が令和7年度に表示している値と一致する）</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>令和7年度の実績で固定した</t>
+          <t>**令和8年10月1日に要介護度別に改め、据え置きを解消した。**従前は要支援・要介護の群でまとめた1人1月あたりで置いていた</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>回数のみでは月額への効きは小さい</t>
+          <t>給付費には入らないため月額への効きはない。延べの回（日）数が最大＋0.09％（訪問介護）動く</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>国の様式も見える化システムも要介護度別の推計を出力しない</t>
+          <t>国の様式も見える化システムも要介護度別の推計を出力しない。令和8年度は4か月分（月報）しかなく、構成を取り直す基礎にならない（令和8年10月1日に再確認した）</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額+8円</t>
+          <t>一律の伸びとの差は月額+10円</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3は令和7年度（完結年度）を基準とする</t>
+          <t>採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である（令和8年10月1日に再確認した）</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない</t>
+          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。**基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない**</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>9,031,900,444円</t>
+          <t>9,035,114,142円</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額+8円です。</t>
+          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額+10円です。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -13352,16 +13352,16 @@
         <v>14965.1</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>15285.4</v>
+        <v>15292.1</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>15449.3</v>
+        <v>15459.3</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>15615.7</v>
+        <v>15629.2</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>1.043</v>
+        <v>1.044</v>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
     </row>
@@ -13414,13 +13414,13 @@
         <v>1076</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1098.7</v>
+        <v>1098.8</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>1110.3</v>
+        <v>1110.4</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>1122.1</v>
+        <v>1122.3</v>
       </c>
       <c r="H24" s="19" t="n">
         <v>1.043</v>
@@ -13445,13 +13445,13 @@
         <v>764.7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>780.7</v>
+        <v>780.8</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>788.9</v>
+        <v>789</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>797.2</v>
+        <v>797.4</v>
       </c>
       <c r="H25" s="19" t="n">
         <v>1.043</v>
@@ -13476,13 +13476,13 @@
         <v>850.6</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>868.5</v>
+        <v>868.6</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>877.7</v>
+        <v>877.9</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>887</v>
+        <v>887.2</v>
       </c>
       <c r="H26" s="19" t="n">
         <v>1.043</v>
@@ -13507,13 +13507,13 @@
         <v>600.7</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>613.3</v>
+        <v>613.5</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>619.8</v>
+        <v>620</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>626.4</v>
+        <v>626.7</v>
       </c>
       <c r="H27" s="19" t="n">
         <v>1.043</v>
@@ -13538,13 +13538,13 @@
         <v>1354</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>1382.5</v>
+        <v>1382.6</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>1397.1</v>
+        <v>1397.3</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>1411.9</v>
+        <v>1412.2</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>1.043</v>
@@ -13600,13 +13600,13 @@
         <v>100.5</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>103.9</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="H30" s="19" t="n">
         <v>1.045</v>
@@ -13831,27 +13831,27 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>453,541,476</t>
+          <t>453,525,964</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>458,665,092</t>
+          <t>458,641,730</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>463,865,535</t>
+          <t>463,834,258</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>1,376,072,103</t>
+          <t>1,376,001,953</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>15.24％</t>
+          <t>15.23％</t>
         </is>
       </c>
     </row>
@@ -13876,27 +13876,27 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>208,670,837</t>
+          <t>208,640,953</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>210,989,927</t>
+          <t>210,945,016</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>213,344,003</t>
+          <t>213,284,004</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>633,004,768</t>
+          <t>632,869,974</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>7.01％</t>
+          <t>7.00％</t>
         </is>
       </c>
     </row>
@@ -13921,22 +13921,22 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>491,892,163</t>
+          <t>491,933,322</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>497,298,152</t>
+          <t>497,360,096</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>502,786,249</t>
+          <t>502,869,121</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1,491,976,564</t>
+          <t>1,492,162,538</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -13966,22 +13966,22 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>27,549,852</t>
+          <t>27,549,632</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>27,827,685</t>
+          <t>27,827,354</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>28,110,010</t>
+          <t>28,109,568</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>83,487,548</t>
+          <t>83,486,554</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -14056,22 +14056,22 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>129,581,606</t>
+          <t>129,639,501</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>130,948,394</t>
+          <t>131,036,280</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>132,335,556</t>
+          <t>132,454,148</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>392,865,557</t>
+          <t>393,129,928</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -14146,22 +14146,22 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>271,540,817</t>
+          <t>271,575,689</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>274,544,059</t>
+          <t>274,596,535</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>277,592,844</t>
+          <t>277,663,044</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>823,677,720</t>
+          <t>823,835,268</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -14191,22 +14191,22 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>441,579,831</t>
+          <t>441,780,567</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>446,314,791</t>
+          <t>446,616,937</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>451,122,834</t>
+          <t>451,527,124</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>1,339,017,456</t>
+          <t>1,339,924,628</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -14236,22 +14236,22 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>5,184,660</t>
+          <t>5,182,370</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>5,239,019</t>
+          <t>5,235,577</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>5,294,230</t>
+          <t>5,289,631</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15,717,909</t>
+          <t>15,707,578</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -14281,22 +14281,22 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>61,764,796</t>
+          <t>61,787,644</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>62,411,280</t>
+          <t>62,446,205</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>63,067,514</t>
+          <t>63,114,957</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>187,243,590</t>
+          <t>187,348,806</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -14326,22 +14326,22 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>27,025,437</t>
+          <t>27,031,900</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>27,308,594</t>
+          <t>27,318,368</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>27,595,998</t>
+          <t>27,609,137</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>81,930,029</t>
+          <t>81,959,405</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -14371,22 +14371,22 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>23,367,113</t>
+          <t>23,365,287</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>23,620,294</t>
+          <t>23,617,525</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>23,877,306</t>
+          <t>23,873,576</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>70,864,714</t>
+          <t>70,856,388</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -14416,22 +14416,22 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>74,295,341</t>
+          <t>74,313,673</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>75,081,156</t>
+          <t>75,108,743</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>75,879,178</t>
+          <t>75,916,084</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>225,255,675</t>
+          <t>225,338,500</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -14461,22 +14461,22 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>62,952,665</t>
+          <t>62,989,089</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>63,618,186</t>
+          <t>63,672,994</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>64,294,048</t>
+          <t>64,367,359</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>190,864,898</t>
+          <t>191,029,442</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>184,763,050</t>
+          <t>184,847,887</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>186,656,367</t>
+          <t>186,785,013</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>188,577,814</t>
+          <t>188,751,222</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>559,997,231</t>
+          <t>560,384,121</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -14551,22 +14551,22 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>28,227,029</t>
+          <t>28,233,578</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>28,532,940</t>
+          <t>28,542,848</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>28,843,470</t>
+          <t>28,856,796</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>85,603,439</t>
+          <t>85,633,221</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>15,217,602</t>
+          <t>15,223,080</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>15,385,423</t>
+          <t>15,393,676</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>15,555,767</t>
+          <t>15,566,821</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>46,158,792</t>
+          <t>46,183,576</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -14731,22 +14731,22 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>78,241,889</t>
+          <t>78,281,470</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>79,053,722</t>
+          <t>79,113,753</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>79,877,582</t>
+          <t>79,958,513</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>237,173,193</t>
+          <t>237,353,736</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -14776,22 +14776,22 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>5,274,250</t>
+          <t>5,275,364</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>5,328,124</t>
+          <t>5,329,811</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>5,382,791</t>
+          <t>5,385,063</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>15,985,165</t>
+          <t>15,990,237</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -14821,22 +14821,22 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>8,485,920</t>
+          <t>8,486,122</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>8,571,450</t>
+          <t>8,571,749</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>8,658,223</t>
+          <t>8,658,615</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>25,715,593</t>
+          <t>25,716,486</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -14866,22 +14866,22 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>1,934,819</t>
+          <t>1,935,059</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>1,954,098</t>
+          <t>1,954,461</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>1,973,690</t>
+          <t>1,974,177</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>5,862,607</t>
+          <t>5,863,696</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -15001,27 +15001,27 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>239,011,293</t>
+          <t>239,151,481</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>241,530,331</t>
+          <t>241,742,299</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>244,087,623</t>
+          <t>244,372,529</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>724,629,247</t>
+          <t>725,266,309</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>8.02％</t>
+          <t>8.03％</t>
         </is>
       </c>
     </row>
@@ -15091,22 +15091,22 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>136,964,030</t>
+          <t>137,023,991</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>138,377,051</t>
+          <t>138,468,439</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>139,811,097</t>
+          <t>139,934,898</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>415,152,178</t>
+          <t>415,427,328</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -15130,22 +15130,22 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>9,031,900,444</t>
+          <t>9,035,114,142</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -15209,27 +15209,27 @@
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>1,181,654,328</t>
+          <t>1,181,649,871</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>1,194,780,856</t>
+          <t>1,194,774,196</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>1,208,105,798</t>
+          <t>1,208,096,951</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>3,584,540,982</t>
+          <t>3,584,521,018</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>39.69％</t>
+          <t>39.67％</t>
         </is>
       </c>
     </row>
@@ -15246,22 +15246,22 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>401,122,424</t>
+          <t>401,215,190</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>405,492,453</t>
+          <t>405,632,815</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>409,928,400</t>
+          <t>410,117,191</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>1,216,543,277</t>
+          <t>1,216,965,196</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -15283,27 +15283,27 @@
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1,395,491,141</t>
+          <t>1,396,109,980</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>1,410,197,584</t>
+          <t>1,411,133,153</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>1,425,127,460</t>
+          <t>1,426,384,795</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>4,230,816,185</t>
+          <t>4,233,627,928</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>46.84％</t>
+          <t>46.86％</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>注1）ここでいう給付費は総給付費であり、特定入所者介護サービス費・高額介護サービス費・審査支払手数料等を含みません。これらを加えたものが標準給付費見込額です（13シート）。
-注2）令和7年度の総給付費は2,915,307,125円です。第10期の3か年計は9,031,900,444円で、令和7年度の3年分に対し+3.3％です。
+注2）令和7年度の総給付費は2,915,307,125円です。第10期の3か年計は9,035,114,142円で、令和7年度の3年分に対し+3.3％です。
 注3）1人あたり給付費は延べ1人あたりの月額です。令和7年度の実績で固定しています。</t>
         </is>
       </c>
@@ -17581,7 +17581,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -17591,12 +17591,12 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>707,147</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+0.024％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -17629,12 +17629,12 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>1,069,271</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>+0.036％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -17667,12 +17667,12 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>1,437,280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+0.047％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>3,066,588,037</t>
+          <t>3,068,203,871</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>1,615,834</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>+0.053％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,317,848,527</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -17743,12 +17743,12 @@
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>7,725,692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>+0.233％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr"/>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>3,408,932,536</t>
+          <t>3,418,469,468</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
@@ -17781,12 +17781,12 @@
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>9,536,931</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>+0.280％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr"/>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>3,258,825,048</t>
+          <t>3,265,402,536</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -17819,12 +17819,12 @@
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>6,577,487</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>+0.202％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr"/>
@@ -17847,7 +17847,7 @@
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>3,240,335,214</t>
+          <t>3,245,610,859</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -17857,12 +17857,12 @@
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
-          <t>5,275,646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>+0.163％</t>
+          <t>+0.000％</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr"/>
@@ -17878,7 +17878,7 @@
       <c r="A68" s="10" t="inlineStr">
         <is>
           <t>注1）06シートは種別ごとの単価（延べ1人あたり）を令和7年度で固定しています。要介護度別の単価を用いると、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
-注2）効きは第10期では小さく（令和11年度で+0.047％）、算定上の月額基準額で+2.2円です。令和22年度では+0.280％に開きます。
+注2）効きは第10期では小さく（令和11年度で+0.000％）、算定上の月額基準額で+0.0円です。令和22年度では+0.000％に開きます。
 注3）本表の採用値は06シート（単価固定）のままとしています。ツールの要介護度別の値は3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていないためです。［要確認］</t>
         </is>
       </c>

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -6051,7 +6051,7 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>注1）改定率1％あたり月額+61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
+          <t>注1）改定率1％あたり月額＋61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
 注2）本表の改定率は1回分の改定を見たものです。第10期の期間中の改定は令和9年度のみです（次は令和12年度）が、基準年度である令和7年度の単価には令和8年度改定も反映されていないため、令和7年度の単価から見れば2回分の改定が織り込まれていません。2回分を織り込む場合は、本表の改定率を2回分の合計として読みます。
 注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
 注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
@@ -6380,17 +6380,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の将来推計</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>国の様式も見える化システムも要介護度別の推計を出力しない。令和8年度は4か月分（月報）しかなく、構成を取り直す基礎にならない（令和8年10月1日に再確認した）</t>
+          <t>国の様式も見える化システムも要介護度別の推計を出力しない。基礎となり得るのは年報の年齢階級別×要介護度の表だけであり、令和8年度は4か月分（月報）で、かつ月報は年齢階級別×要介護度を持たないため構成を取り直せない</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される</t>
+          <t>**令和8年10月1日に確定した。**年齢階級ごとの要介護度の構成を令和7年度末（年報 様式1の5）の実績で固定し、将来推計 第1段階の年齢階級別認定者数に乗じる。年齢構成の変化による重度化は反映され、要介護度別の和は第1段階の認定者数と完全に一致する（点検3・点検11）</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額+10円</t>
+          <t>一律の伸びとの差は月額＋10円</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である（令和8年10月1日に再確認した）</t>
+          <t>採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。**基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない**</t>
+          <t>**令和8年10月1日に確定した。**季節補正を行わない。基準年度が12か月の完結年度であるため季節指数の和は12となり、年度換算係数は12÷12＝1.0000で恒等的に消える。**季節性を測定できるようになっても採用値は動かない**ため、資料の受領を待たない</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額+10円です。</t>
+          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額＋10円です。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -5808,7 +5808,7 @@
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>注1）第9期は財政調整基金40,000,000円を取り崩しています。本表は取崩しを行わないものとしています。同額を取り崩せば月額は約▲124円となります。
-注2）据え置いたもの（15シート）のうち、報酬改定率と単価の趨勢は月額を＋185〜＋374円動かし得ます。本表の月額はこれを含まない下側の値です。
+注2）据え置いたもの（15シート）のうち、報酬改定率と単価の趨勢は月額を＋245円〜＋327円動かし得ます。本表の月額はこれを含まない下側の値です。
 注3）第1号被保険者負担割合を23％で置いています。1ポイントの違いで月額が約290円動きます。［要確認］</t>
         </is>
       </c>
@@ -6053,7 +6053,7 @@
         <is>
           <t>注1）改定率1％あたり月額＋61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
 注2）本表の改定率は1回分の改定を見たものです。第10期の期間中の改定は令和9年度のみです（次は令和12年度）が、基準年度である令和7年度の単価には令和8年度改定も反映されていないため、令和7年度の単価から見れば2回分の改定が織り込まれていません。2回分を織り込む場合は、本表の改定率を2回分の合計として読みます。
-注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
+注3）単価は改定の有無に関係なく年率1.75％（中央値1.32％）で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋245円〜＋327円に当たります。
 注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
         </is>
       </c>
@@ -6133,14 +6133,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9351.299999999999</v>
+        <v>9352.200000000001</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6651</v>
+        <v>6652</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>+213円</t>
+          <t>+214円</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>9520</v>
+        <v>9521.299999999999</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6765</v>
+        <v>6766</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>令和9年度＋3.53％・令和10年度＋5.34％・令和11年度＋7.22％</t>
+          <t>令和9年度＋3.54％・令和10年度＋5.36％・令和11年度＋7.21％</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋185〜＋374円に当たる</t>
+          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たる</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>注1）23件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋185〜＋374円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
+          <t>注1）23件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋245円〜＋327円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
 注2）安全側に置いたもの（保険料が不足する側に誤らないようにしたもの）は3件です。施策の反映を織り込まない、給付適正化による抑制を織り込まない、施設・居住系の定員の縮小を将来へ延長しない、の3件です。
 注3）対計画比は第7期からの8年度すべてで100％未満（8年平均94.93％）であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため、同じ偏りを持ち得ます（確認事項No.106）。</t>
         </is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋185〜＋374円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
+          <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋245円〜＋327円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -662,7 +662,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを15シートに残らず掲げています。受託者の算定であり確定値ではありません。（基準日 令和8年9月15日）</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを15シートに残らず掲げています。ご決定をお待ちしている事項は、決着しない場合の扱い（既定値）によって算定しています（確認事項No.142）。既定値は受託者の仮置きであり、ご決定の内容が異なる場合はその内容により置き直します。受託者の算定であり確定値ではありません。（基準日 令和8年10月1日）</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たる</t>
+          <t>改定率1％あたり月額＋61円。単価の年率1.32％から1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たり、令和8年度の水準（残差＋1.63％）に置くと月額＋99円（確認事項No.104）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第1次概算.xlsx
@@ -662,7 +662,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを15シートに残らず掲げています。ご決定をお待ちしている事項は、決着しない場合の扱い（既定値）によって算定しています（確認事項No.142）。既定値は受託者の仮置きであり、ご決定の内容が異なる場合はその内容により置き直します。受託者の算定であり確定値ではありません。（基準日 令和8年10月1日）</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたものです。決着していない事項は過年度（令和7年度又は令和6年度）の数値を据え置き、据え置いたものを15シートに残らず掲げています。受託者の算定であり確定値ではありません。（基準日 令和8年9月15日）</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>9,035,114,142円</t>
+          <t>9,031,900,444円</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>6,438円</t>
+          <t>6,436円</t>
         </is>
       </c>
     </row>
@@ -4653,36 +4653,36 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>3,044,598,937</t>
+          <t>3,043,161,657</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>3,068,203,871</t>
+          <t>3,066,588,037</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>3,317,848,527</t>
+          <t>3,310,122,835</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>3,418,469,468</t>
+          <t>3,408,932,536</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>3,265,402,536</t>
+          <t>3,258,825,048</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>3,245,610,859</t>
+          <t>3,240,335,214</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
-        <v>1.113</v>
+        <v>1.111</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>3,044,598,937</t>
+          <t>3,043,161,657</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>9213</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>6481</v>
+        <v>6478</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>3,068,203,871</t>
+          <t>3,066,588,037</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>9211</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>6530</v>
+        <v>6527</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
@@ -4809,18 +4809,18 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>3,317,848,527</t>
+          <t>3,310,122,835</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>9250</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>7003</v>
+        <v>6988</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+510</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -4842,18 +4842,18 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>3,418,469,468</t>
+          <t>3,408,932,536</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>9491</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>7022</v>
+        <v>7003</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>+541</t>
+          <t>+525</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -4875,18 +4875,18 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>3,265,402,536</t>
+          <t>3,258,825,048</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>9395</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>6792</v>
+        <v>6779</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>+311</t>
+          <t>+300</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -4908,18 +4908,18 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>3,245,610,859</t>
+          <t>3,240,335,214</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>9127</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>6951</v>
+        <v>6940</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+462</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9,035,114,142</t>
+          <t>9,031,900,444</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>14,885,261</t>
+          <t>11,671,563</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>9,569,019,924</t>
+          <t>9,565,616,321</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>15,764,866</t>
+          <t>12,361,263</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>10,100,503,701</t>
+          <t>10,097,100,098</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>15,764,866</t>
+          <t>12,361,263</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>9,890,407,878</t>
+          <t>9,887,004,275</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>15,764,866</t>
+          <t>12,361,263</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2,323,115,851</t>
+          <t>2,322,333,022</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>3,625,919</t>
+          <t>2,843,090</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>494,520,394</t>
+          <t>494,350,214</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>788,243</t>
+          <t>618,063</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>729,464,444</t>
+          <t>729,213,412</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1,162,734</t>
+          <t>911,702</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2,088,171,801</t>
+          <t>2,087,469,824</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>3,251,429</t>
+          <t>2,549,452</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>6,438円</t>
+          <t>6,436円</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>+10円</t>
+          <t>+8円</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -5542,22 +5542,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2,978,975,041</t>
+          <t>2,978,267,893</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>3,011,540,164</t>
+          <t>3,010,470,894</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>3,044,598,937</t>
+          <t>3,043,161,657</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>9,035,114,142</t>
+          <t>9,031,900,444</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5672,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>9,569,019,924</t>
+          <t>9,565,616,321</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>49,808,400（+0.5％）</t>
+          <t>46,404,797（+0.5％）</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>2,088,171,801</t>
+          <t>2,087,469,824</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>36,203,334（+1.8％）</t>
+          <t>35,501,357（+1.7％）</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>6,438円</t>
+          <t>6,436円</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>+10円（+0.2％）</t>
+          <t>+8円（+0.1％）</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
@@ -5808,7 +5808,7 @@
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>注1）第9期は財政調整基金40,000,000円を取り崩しています。本表は取崩しを行わないものとしています。同額を取り崩せば月額は約▲124円となります。
-注2）据え置いたもの（15シート）のうち、報酬改定率と単価の趨勢は月額を＋245円〜＋327円動かし得ます。本表の月額はこれを含まない下側の値です。
+注2）据え置いたもの（15シート）のうち、報酬改定率と単価の趨勢は月額を＋185〜＋374円動かし得ます。本表の月額はこれを含まない下側の値です。
 注3）第1号被保険者負担割合を23％で置いています。1ポイントの違いで月額が約290円動きます。［要確認］</t>
         </is>
       </c>
@@ -5855,7 +5855,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和9年度は介護報酬改定の年に当たります（3年周期）。加えて、令和9年度改定を待たずに令和8年度にも改定が行われることが令和8年3月の全国課長会議資料に示されています。いずれも改定率が未公表であるため単価を令和7年度で固定していますが、改定率を一律に乗じた場合に月額がどこまで動くかを示します。</t>
+          <t>令和9年度は介護報酬改定の年に当たります（3年周期）。改定率が未公表であるため単価を令和7年度で固定していますが、改定率を一律に乗じた場合に月額がどこまで動くかを示します。</t>
         </is>
       </c>
     </row>
@@ -5915,24 +5915,24 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2,978,975,041</t>
+          <t>2,978,267,893</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>3,011,540,164</t>
+          <t>3,010,470,894</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>3,044,598,937</t>
+          <t>3,043,161,657</t>
         </is>
       </c>
       <c r="F6" s="31" t="n">
-        <v>9035.1</v>
+        <v>9031.9</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>6438</v>
+        <v>6436</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -5951,24 +5951,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3,008,764,791</t>
+          <t>3,008,050,572</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>3,041,655,566</t>
+          <t>3,040,575,602</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>3,075,044,927</t>
+          <t>3,073,593,274</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>9125.5</v>
+        <v>9122.200000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>6499</v>
+        <v>6497</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -5987,24 +5987,24 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3,038,554,541</t>
+          <t>3,037,833,251</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>3,071,770,968</t>
+          <t>3,070,680,311</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>3,105,490,916</t>
+          <t>3,104,024,890</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9215.799999999999</v>
+        <v>9212.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6560</v>
+        <v>6558</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -6023,37 +6023,37 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>3,068,344,292</t>
+          <t>3,067,615,930</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>3,101,886,369</t>
+          <t>3,100,785,020</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>3,135,936,905</t>
+          <t>3,134,456,507</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>9306.200000000001</v>
+        <v>9302.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6621</v>
+        <v>6619</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>+183円</t>
+          <t>+182円</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>注1）改定率1％あたり月額＋61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
-注2）本表の改定率は1回分の改定を見たものです。第10期の期間中の改定は令和9年度のみです（次は令和12年度）が、基準年度である令和7年度の単価には令和8年度改定も反映されていないため、令和7年度の単価から見れば2回分の改定が織り込まれていません。2回分を織り込む場合は、本表の改定率を2回分の合計として読みます。
-注3）単価は改定の有無に関係なく年率1.75％（中央値1.32％）で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋245円〜＋327円に当たります。
+          <t>注1）改定率1％あたり月額+61円です。趨勢に現れない要因の分析（第10章）の＋61円と一致します。
+注2）改定は令和9年度の1回だけを見ています。第10期中の改定は令和9年度のみです（次は令和12年度）。
+注3）単価は改定の有無に関係なく年率1.75％で伸びています（構成を固定した連鎖ラスパイレス指数で7年＋12.93％。改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。単価を令和7年度で固定していることは、改定率とは別に月額で＋185〜＋374円に当たります。
 注4）本表の採用値は改定率0％（単価固定）のままとしています。改定率が公表された時点で置き直します。［要協議］</t>
         </is>
       </c>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9035.1</v>
+        <v>9031.9</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6438</v>
+        <v>6436</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
@@ -6133,14 +6133,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9352.200000000001</v>
+        <v>9348</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6652</v>
+        <v>6649</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>+214円</t>
+          <t>+213円</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -6161,21 +6161,21 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>9521.299999999999</v>
+        <v>9516.6</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6766</v>
+        <v>6762</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>+327円</t>
+          <t>+326円</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>令和9年度＋3.54％・令和10年度＋5.36％・令和11年度＋7.21％</t>
+          <t>令和9年度＋3.53％・令和10年度＋5.34％・令和11年度＋7.22％</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>令和9年度は報酬改定の年に当たるが改定率は未公表である。加えて令和8年度にも改定が行われるため、令和7年度の単価は2回分の改定を織り込んでいない</t>
+          <t>令和9年度は報酬改定の年に当たるが改定率は未公表である</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>改定率1％あたり月額＋61円。単価の年率1.32％から1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たり、令和8年度の水準（残差＋1.63％）に置くと月額＋99円（確認事項No.104）</t>
+          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋185〜＋374円に当たる</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（４）は要介護度別の内訳を持たない。要介護度間の比は給付費データ（保険者単位）から採れる（従前「計画作成支援ツールは3町合計であり比が保険者単位でも同じかは未確認」としていたのは当たらない）</t>
+          <t>総括表詳細（４）は要介護度別の内訳を持たない。計画作成支援ツールは要介護度別を持つが3町合計である</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>**令和8年10月1日に採用し、据え置きを解消した。**要介護度間の比を給付費データ（保険者単位）から採り、水準は総括表に合わせて比例調整している。基準年度では総括表の給付費を円単位で再現する（点検16）</t>
+          <t>ツールから要介護度間の比（形）だけを採り、水準は総括表に合わせて比例調整した。採用値は単価固定（06シート）のままとし、07シートに別掲した</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>採用により総給付費（3か年）＋3,213,698円・月額＋2.17円。保険料基準額は6,400円で変わらない</t>
+          <t>要介護度別の単価を用いると令和11年度＋0.047％（月額＋2円）、令和22年度＋0.280％</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>年報の要介護度別の明細により要介護度別に求められる（見える化システムの画面が令和7年度に表示している値と一致する）</t>
+          <t>同上。回数の趨勢は年率＋0.25％（中央値）にとどまる</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>**令和8年10月1日に要介護度別に改め、据え置きを解消した。**従前は要支援・要介護の群でまとめた1人1月あたりで置いていた</t>
+          <t>令和7年度の実績で固定した</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>給付費には入らないため月額への効きはない。延べの回（日）数が最大＋0.09％（訪問介護）動く</t>
+          <t>回数のみでは月額への効きは小さい</t>
         </is>
       </c>
     </row>
@@ -6380,27 +6380,27 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
+          <t>要介護度別の将来推計</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>国の様式も見える化システムも要介護度別の推計を出力しない</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>国の様式も見える化システムも要介護度別の推計を出力しない。基礎となり得るのは年報の年齢階級別×要介護度の表だけであり、令和8年度は4か月分（月報）で、かつ月報は年齢階級別×要介護度を持たないため構成を取り直せない</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>**令和8年10月1日に確定した。**年齢階級ごとの要介護度の構成を令和7年度末（年報 様式1の5）の実績で固定し、将来推計 第1段階の年齢階級別認定者数に乗じる。年齢構成の変化による重度化は反映され、要介護度別の和は第1段階の認定者数と完全に一致する（点検3・点検11）</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額＋10円</t>
+          <t>一律の伸びとの差は月額+8円</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である</t>
+          <t>採用パターンP3は令和7年度（完結年度）を基準とする</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>**令和8年10月1日に確定した。**季節補正を行わない。基準年度が12か月の完結年度であるため季節指数の和は12となり、年度換算係数は12÷12＝1.0000で恒等的に消える。**季節性を測定できるようになっても採用値は動かない**ため、資料の受領を待たない</t>
+          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>注1）23件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋245円〜＋327円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
+          <t>注1）23件のうち、月額を100円以上動かし得るものは報酬改定率・単価の趨勢（＋185〜＋374円）、第1号被保険者負担割合（1ポイントで約290円）、基金の取崩し（1億円で約▲310円）の3件です。
 注2）安全側に置いたもの（保険料が不足する側に誤らないようにしたもの）は3件です。施策の反映を織り込まない、給付適正化による抑制を織り込まない、施設・居住系の定員の縮小を将来へ延長しない、の3件です。
 注3）対計画比は第7期からの8年度すべてで100％未満（8年平均94.93％）であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため、同じ偏りを持ち得ます（確認事項No.106）。</t>
         </is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>9,035,114,142円</t>
+          <t>9,031,900,444円</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額＋10円です。</t>
+          <t>従前の採用パターンP3は認定者数の総数による一律の伸びでした。年報（令和7年度）の要介護度別の明細を収めたことにより、要介護度別に利用率を固定して延ばすことができるようになりました。国の様式も見える化システムも要介護度別の入力を求めます。一律の伸びとの差は月額+8円です。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋245円〜＋327円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
+          <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋185〜＋374円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -13352,16 +13352,16 @@
         <v>14965.1</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>15292.1</v>
+        <v>15285.4</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>15459.3</v>
+        <v>15449.3</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>15629.2</v>
+        <v>15615.7</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>1.044</v>
+        <v>1.043</v>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
     </row>
@@ -13414,13 +13414,13 @@
         <v>1076</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1098.8</v>
+        <v>1098.7</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>1110.4</v>
+        <v>1110.3</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>1122.3</v>
+        <v>1122.1</v>
       </c>
       <c r="H24" s="19" t="n">
         <v>1.043</v>
@@ -13445,13 +13445,13 @@
         <v>764.7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>780.8</v>
+        <v>780.7</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>789</v>
+        <v>788.9</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>797.4</v>
+        <v>797.2</v>
       </c>
       <c r="H25" s="19" t="n">
         <v>1.043</v>
@@ -13476,13 +13476,13 @@
         <v>850.6</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>868.6</v>
+        <v>868.5</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>877.9</v>
+        <v>877.7</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>887.2</v>
+        <v>887</v>
       </c>
       <c r="H26" s="19" t="n">
         <v>1.043</v>
@@ -13507,13 +13507,13 @@
         <v>600.7</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>613.5</v>
+        <v>613.3</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>620</v>
+        <v>619.8</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>626.7</v>
+        <v>626.4</v>
       </c>
       <c r="H27" s="19" t="n">
         <v>1.043</v>
@@ -13538,13 +13538,13 @@
         <v>1354</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>1382.6</v>
+        <v>1382.5</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>1397.3</v>
+        <v>1397.1</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>1412.2</v>
+        <v>1411.9</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>1.043</v>
@@ -13600,13 +13600,13 @@
         <v>100.5</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>102.8</v>
+        <v>102.7</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>103.9</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="H30" s="19" t="n">
         <v>1.045</v>
@@ -13831,27 +13831,27 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>453,525,964</t>
+          <t>453,541,476</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>458,641,730</t>
+          <t>458,665,092</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>463,834,258</t>
+          <t>463,865,535</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>1,376,001,953</t>
+          <t>1,376,072,103</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>15.23％</t>
+          <t>15.24％</t>
         </is>
       </c>
     </row>
@@ -13876,27 +13876,27 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>208,640,953</t>
+          <t>208,670,837</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>210,945,016</t>
+          <t>210,989,927</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>213,284,004</t>
+          <t>213,344,003</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>632,869,974</t>
+          <t>633,004,768</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>7.00％</t>
+          <t>7.01％</t>
         </is>
       </c>
     </row>
@@ -13921,22 +13921,22 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>491,933,322</t>
+          <t>491,892,163</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>497,360,096</t>
+          <t>497,298,152</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>502,869,121</t>
+          <t>502,786,249</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1,492,162,538</t>
+          <t>1,491,976,564</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -13966,22 +13966,22 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>27,549,632</t>
+          <t>27,549,852</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>27,827,354</t>
+          <t>27,827,685</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>28,109,568</t>
+          <t>28,110,010</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>83,486,554</t>
+          <t>83,487,548</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -14056,22 +14056,22 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>129,639,501</t>
+          <t>129,581,606</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>131,036,280</t>
+          <t>130,948,394</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>132,454,148</t>
+          <t>132,335,556</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>393,129,928</t>
+          <t>392,865,557</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -14146,22 +14146,22 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>271,575,689</t>
+          <t>271,540,817</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>274,596,535</t>
+          <t>274,544,059</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>277,663,044</t>
+          <t>277,592,844</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>823,835,268</t>
+          <t>823,677,720</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -14191,22 +14191,22 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>441,780,567</t>
+          <t>441,579,831</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>446,616,937</t>
+          <t>446,314,791</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>451,527,124</t>
+          <t>451,122,834</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>1,339,924,628</t>
+          <t>1,339,017,456</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -14236,22 +14236,22 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>5,182,370</t>
+          <t>5,184,660</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>5,235,577</t>
+          <t>5,239,019</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>5,289,631</t>
+          <t>5,294,230</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15,707,578</t>
+          <t>15,717,909</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -14281,22 +14281,22 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>61,787,644</t>
+          <t>61,764,796</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>62,446,205</t>
+          <t>62,411,280</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>63,114,957</t>
+          <t>63,067,514</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>187,348,806</t>
+          <t>187,243,590</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -14326,22 +14326,22 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>27,031,900</t>
+          <t>27,025,437</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>27,318,368</t>
+          <t>27,308,594</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>27,609,137</t>
+          <t>27,595,998</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>81,959,405</t>
+          <t>81,930,029</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -14371,22 +14371,22 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>23,365,287</t>
+          <t>23,367,113</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>23,617,525</t>
+          <t>23,620,294</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>23,873,576</t>
+          <t>23,877,306</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>70,856,388</t>
+          <t>70,864,714</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -14416,22 +14416,22 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>74,313,673</t>
+          <t>74,295,341</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>75,108,743</t>
+          <t>75,081,156</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>75,916,084</t>
+          <t>75,879,178</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>225,338,500</t>
+          <t>225,255,675</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -14461,22 +14461,22 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>62,989,089</t>
+          <t>62,952,665</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>63,672,994</t>
+          <t>63,618,186</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>64,367,359</t>
+          <t>64,294,048</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>191,029,442</t>
+          <t>190,864,898</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>184,847,887</t>
+          <t>184,763,050</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>186,785,013</t>
+          <t>186,656,367</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>188,751,222</t>
+          <t>188,577,814</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>560,384,121</t>
+          <t>559,997,231</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -14551,22 +14551,22 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>28,233,578</t>
+          <t>28,227,029</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>28,542,848</t>
+          <t>28,532,940</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>28,856,796</t>
+          <t>28,843,470</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>85,633,221</t>
+          <t>85,603,439</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>15,223,080</t>
+          <t>15,217,602</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>15,393,676</t>
+          <t>15,385,423</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>15,566,821</t>
+          <t>15,555,767</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>46,183,576</t>
+          <t>46,158,792</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -14731,22 +14731,22 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>78,281,470</t>
+          <t>78,241,889</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>79,113,753</t>
+          <t>79,053,722</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>79,958,513</t>
+          <t>79,877,582</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>237,353,736</t>
+          <t>237,173,193</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -14776,22 +14776,22 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>5,275,364</t>
+          <t>5,274,250</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>5,329,811</t>
+          <t>5,328,124</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>5,385,063</t>
+          <t>5,382,791</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>15,990,237</t>
+          <t>15,985,165</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -14821,22 +14821,22 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>8,486,122</t>
+          <t>8,485,920</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>8,571,749</t>
+          <t>8,571,450</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>8,658,615</t>
+          <t>8,658,223</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>25,716,486</t>
+          <t>25,715,593</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -14866,22 +14866,22 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>1,935,059</t>
+          <t>1,934,819</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>1,954,461</t>
+          <t>1,954,098</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>1,974,177</t>
+          <t>1,973,690</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>5,863,696</t>
+          <t>5,862,607</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -15001,27 +15001,27 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>239,151,481</t>
+          <t>239,011,293</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>241,742,299</t>
+          <t>241,530,331</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>244,372,529</t>
+          <t>244,087,623</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>725,266,309</t>
+          <t>724,629,247</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>8.03％</t>
+          <t>8.02％</t>
         </is>
       </c>
     </row>
@@ -15091,22 +15091,22 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>137,023,991</t>
+          <t>136,964,030</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>138,468,439</t>
+          <t>138,377,051</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>139,934,898</t>
+          <t>139,811,097</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>415,427,328</t>
+          <t>415,152,178</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -15130,22 +15130,22 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2,978,975,041</t>
+          <t>2,978,267,893</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>3,011,540,164</t>
+          <t>3,010,470,894</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>3,044,598,937</t>
+          <t>3,043,161,657</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>9,035,114,142</t>
+          <t>9,031,900,444</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -15209,27 +15209,27 @@
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>1,181,649,871</t>
+          <t>1,181,654,328</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>1,194,774,196</t>
+          <t>1,194,780,856</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>1,208,096,951</t>
+          <t>1,208,105,798</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>3,584,521,018</t>
+          <t>3,584,540,982</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>39.67％</t>
+          <t>39.69％</t>
         </is>
       </c>
     </row>
@@ -15246,22 +15246,22 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>401,215,190</t>
+          <t>401,122,424</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>405,632,815</t>
+          <t>405,492,453</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>410,117,191</t>
+          <t>409,928,400</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>1,216,965,196</t>
+          <t>1,216,543,277</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -15283,27 +15283,27 @@
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1,396,109,980</t>
+          <t>1,395,491,141</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>1,411,133,153</t>
+          <t>1,410,197,584</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>1,426,384,795</t>
+          <t>1,425,127,460</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>4,233,627,928</t>
+          <t>4,230,816,185</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>46.86％</t>
+          <t>46.84％</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>注1）ここでいう給付費は総給付費であり、特定入所者介護サービス費・高額介護サービス費・審査支払手数料等を含みません。これらを加えたものが標準給付費見込額です（13シート）。
-注2）令和7年度の総給付費は2,915,307,125円です。第10期の3か年計は9,035,114,142円で、令和7年度の3年分に対し+3.3％です。
+注2）令和7年度の総給付費は2,915,307,125円です。第10期の3か年計は9,031,900,444円で、令和7年度の3年分に対し+3.3％です。
 注3）1人あたり給付費は延べ1人あたりの月額です。令和7年度の実績で固定しています。</t>
         </is>
       </c>
@@ -17581,22 +17581,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
+          <t>2,978,267,893</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
           <t>2,978,975,041</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>2,978,975,041</t>
-        </is>
-      </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>707,147</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.024％</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -17619,22 +17619,22 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
+          <t>3,010,470,894</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
           <t>3,011,540,164</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>3,011,540,164</t>
-        </is>
-      </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,069,271</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.036％</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -17657,22 +17657,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
+          <t>3,043,161,657</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
           <t>3,044,598,937</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>3,044,598,937</t>
-        </is>
-      </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,437,280</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.047％</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
+          <t>3,066,588,037</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
           <t>3,068,203,871</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>3,068,203,871</t>
-        </is>
-      </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,615,834</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.053％</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr"/>
@@ -17733,22 +17733,22 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
+          <t>3,310,122,835</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
           <t>3,317,848,527</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>3,317,848,527</t>
-        </is>
-      </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7,725,692</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.233％</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr"/>
@@ -17771,22 +17771,22 @@
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
+          <t>3,408,932,536</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
           <t>3,418,469,468</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>3,418,469,468</t>
-        </is>
-      </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9,536,931</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.280％</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr"/>
@@ -17809,22 +17809,22 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
           <t>3,265,402,536</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>3,265,402,536</t>
-        </is>
-      </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6,577,487</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.202％</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr"/>
@@ -17847,22 +17847,22 @@
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
           <t>3,245,610,859</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>3,245,610,859</t>
-        </is>
-      </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5,275,646</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.163％</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr"/>
@@ -17878,7 +17878,7 @@
       <c r="A68" s="10" t="inlineStr">
         <is>
           <t>注1）06シートは種別ごとの単価（延べ1人あたり）を令和7年度で固定しています。要介護度別の単価を用いると、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
-注2）効きは第10期では小さく（令和11年度で+0.000％）、算定上の月額基準額で+0.0円です。令和22年度では+0.000％に開きます。
+注2）効きは第10期では小さく（令和11年度で+0.047％）、算定上の月額基準額で+2.2円です。令和22年度では+0.280％に開きます。
 注3）本表の採用値は06シート（単価固定）のままとしています。ツールの要介護度別の値は3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていないためです。［要確認］</t>
         </is>
       </c>
